--- a/TBUS_RTM_new.xlsx
+++ b/TBUS_RTM_new.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="600" firstSheet="0" activeTab="3" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DR-FL" sheetId="1" state="visible" r:id="rId1"/>
@@ -234,6 +234,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -263,10 +267,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -636,39 +636,39 @@
           <t>Feature List分解表格</t>
         </is>
       </c>
-      <c r="B1" s="12" t="n"/>
-      <c r="C1" s="12" t="n"/>
-      <c r="D1" s="12" t="n"/>
-      <c r="E1" s="13" t="n"/>
-    </row>
-    <row r="2" ht="21" customHeight="1" s="20">
-      <c r="A2" s="11" t="inlineStr">
+      <c r="B1" s="14" t="n"/>
+      <c r="C1" s="14" t="n"/>
+      <c r="D1" s="14" t="n"/>
+      <c r="E1" s="15" t="n"/>
+    </row>
+    <row r="2" ht="21" customHeight="1" s="22">
+      <c r="A2" s="13" t="inlineStr">
         <is>
           <t>DR编号</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
+      <c r="B2" s="13" t="inlineStr">
         <is>
           <t>Feature类别</t>
         </is>
       </c>
-      <c r="C2" s="11" t="inlineStr">
+      <c r="C2" s="13" t="inlineStr">
         <is>
           <t>FL编号</t>
         </is>
       </c>
-      <c r="D2" s="11" t="inlineStr">
+      <c r="D2" s="13" t="inlineStr">
         <is>
           <t>Feature描述</t>
         </is>
       </c>
-      <c r="E2" s="11" t="inlineStr">
+      <c r="E2" s="13" t="inlineStr">
         <is>
           <t>TP编号</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="27" customHeight="1" s="20">
+    <row r="3" ht="27" customHeight="1" s="22">
       <c r="A3" s="7" t="inlineStr">
         <is>
           <t>DR.APLC.001</t>
@@ -695,7 +695,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="40.5" customHeight="1" s="20">
+    <row r="4" ht="40.5" customHeight="1" s="22">
       <c r="A4" s="7" t="inlineStr">
         <is>
           <t>DR.APLC.001</t>
@@ -722,7 +722,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="94.5" customHeight="1" s="20">
+    <row r="5" ht="94.5" customHeight="1" s="22">
       <c r="A5" s="7" t="inlineStr">
         <is>
           <t>DR.APLC.001</t>
@@ -749,7 +749,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="94.5" customHeight="1" s="20">
+    <row r="6" ht="94.5" customHeight="1" s="22">
       <c r="A6" s="7" t="inlineStr">
         <is>
           <t>DR.APLC.001</t>
@@ -776,7 +776,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="40.5" customHeight="1" s="20">
+    <row r="7" ht="40.5" customHeight="1" s="22">
       <c r="A7" s="7" t="inlineStr">
         <is>
           <t>DR.APLC.001</t>
@@ -803,7 +803,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="54" customHeight="1" s="20">
+    <row r="8" ht="54" customHeight="1" s="22">
       <c r="A8" s="7" t="inlineStr">
         <is>
           <t>DR.APLC.001</t>
@@ -830,7 +830,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="108" customHeight="1" s="20">
+    <row r="9" ht="108" customHeight="1" s="22">
       <c r="A9" s="7" t="inlineStr">
         <is>
           <t>DR.APLC.001</t>
@@ -857,7 +857,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="40.5" customHeight="1" s="20">
+    <row r="10" ht="40.5" customHeight="1" s="22">
       <c r="A10" s="7" t="inlineStr">
         <is>
           <t>DR.APLC.001</t>
@@ -884,7 +884,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="94.5" customHeight="1" s="20">
+    <row r="11" ht="94.5" customHeight="1" s="22">
       <c r="A11" s="7" t="inlineStr">
         <is>
           <t>DR.APLC.001</t>
@@ -911,7 +911,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="40.5" customHeight="1" s="20">
+    <row r="12" ht="40.5" customHeight="1" s="22">
       <c r="A12" s="7" t="inlineStr">
         <is>
           <t>DR.APLC.001</t>
@@ -938,7 +938,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="148.5" customHeight="1" s="20">
+    <row r="13" ht="148.5" customHeight="1" s="22">
       <c r="A13" s="7" t="inlineStr">
         <is>
           <t>DR.APLC.001</t>
@@ -965,7 +965,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="40.5" customHeight="1" s="20">
+    <row r="14" ht="40.5" customHeight="1" s="22">
       <c r="A14" s="7" t="inlineStr">
         <is>
           <t>DR.APLC.001</t>
@@ -992,7 +992,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="67.5" customHeight="1" s="20">
+    <row r="15" ht="67.5" customHeight="1" s="22">
       <c r="A15" s="7" t="inlineStr">
         <is>
           <t>DR.APLC.001</t>
@@ -1019,7 +1019,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="40.5" customHeight="1" s="20">
+    <row r="16" ht="40.5" customHeight="1" s="22">
       <c r="A16" s="7" t="inlineStr">
         <is>
           <t>DR.APLC.001</t>
@@ -1046,7 +1046,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="54" customHeight="1" s="20">
+    <row r="17" ht="54" customHeight="1" s="22">
       <c r="A17" s="7" t="inlineStr">
         <is>
           <t>DR.APLC.001</t>
@@ -1073,7 +1073,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="108" customHeight="1" s="20">
+    <row r="18" ht="108" customHeight="1" s="22">
       <c r="A18" s="7" t="inlineStr">
         <is>
           <t>DR.APLC.001</t>
@@ -1108,18 +1108,18 @@
       <c r="E21" s="0" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="16" t="inlineStr">
+      <c r="A22" s="18" t="inlineStr">
         <is>
           <t>填写说明</t>
         </is>
       </c>
-      <c r="B22" s="17" t="n"/>
-      <c r="C22" s="17" t="n"/>
-      <c r="D22" s="17" t="n"/>
-      <c r="E22" s="18" t="n"/>
-    </row>
-    <row r="23" ht="27.95" customHeight="1" s="20">
-      <c r="A23" s="21" t="inlineStr">
+      <c r="B22" s="19" t="n"/>
+      <c r="C22" s="19" t="n"/>
+      <c r="D22" s="19" t="n"/>
+      <c r="E22" s="20" t="n"/>
+    </row>
+    <row r="23" ht="27.95" customHeight="1" s="22">
+      <c r="A23" s="23" t="inlineStr">
         <is>
           <t>DR编号</t>
         </is>
@@ -1129,12 +1129,12 @@
           <t>应包含’ OR-DR’ sheet中的全部DR；DR-FL可以一对多，也可以多对一； DR编号可以不是顺序的</t>
         </is>
       </c>
-      <c r="C23" s="12" t="n"/>
-      <c r="D23" s="12" t="n"/>
-      <c r="E23" s="13" t="n"/>
-    </row>
-    <row r="24" ht="60" customHeight="1" s="20">
-      <c r="A24" s="21" t="inlineStr">
+      <c r="C23" s="14" t="n"/>
+      <c r="D23" s="14" t="n"/>
+      <c r="E23" s="15" t="n"/>
+    </row>
+    <row r="24" ht="60" customHeight="1" s="22">
+      <c r="A24" s="23" t="inlineStr">
         <is>
           <t>Feature类别</t>
         </is>
@@ -1146,12 +1146,12 @@
 可以重复（例如不同行的Feature类别是相同的）</t>
         </is>
       </c>
-      <c r="C24" s="12" t="n"/>
-      <c r="D24" s="12" t="n"/>
-      <c r="E24" s="13" t="n"/>
-    </row>
-    <row r="25" ht="42.95" customHeight="1" s="20">
-      <c r="A25" s="21" t="inlineStr">
+      <c r="C24" s="14" t="n"/>
+      <c r="D24" s="14" t="n"/>
+      <c r="E24" s="15" t="n"/>
+    </row>
+    <row r="25" ht="42.95" customHeight="1" s="22">
+      <c r="A25" s="23" t="inlineStr">
         <is>
           <t>FL编号</t>
         </is>
@@ -1161,12 +1161,12 @@
           <t>FL_xxx_yyy：其中xxx是Feature类别的编号，yyy是二级feature的编号；</t>
         </is>
       </c>
-      <c r="C25" s="12" t="n"/>
-      <c r="D25" s="12" t="n"/>
-      <c r="E25" s="13" t="n"/>
-    </row>
-    <row r="26" ht="66.95" customHeight="1" s="20">
-      <c r="A26" s="21" t="inlineStr">
+      <c r="C25" s="14" t="n"/>
+      <c r="D25" s="14" t="n"/>
+      <c r="E25" s="15" t="n"/>
+    </row>
+    <row r="26" ht="66.95" customHeight="1" s="22">
+      <c r="A26" s="23" t="inlineStr">
         <is>
           <t>Feature描述</t>
         </is>
@@ -1179,12 +1179,12 @@
 4. 和Design SPEC的配合关系：Feature描述特性，SPEC描述实现方案</t>
         </is>
       </c>
-      <c r="C26" s="12" t="n"/>
-      <c r="D26" s="12" t="n"/>
-      <c r="E26" s="13" t="n"/>
-    </row>
-    <row r="27" ht="29.1" customHeight="1" s="20">
-      <c r="A27" s="21" t="inlineStr">
+      <c r="C26" s="14" t="n"/>
+      <c r="D26" s="14" t="n"/>
+      <c r="E26" s="15" t="n"/>
+    </row>
+    <row r="27" ht="29.1" customHeight="1" s="22">
+      <c r="A27" s="23" t="inlineStr">
         <is>
           <t>TP编号</t>
         </is>
@@ -1194,9 +1194,9 @@
           <t>由DV owner填完FL-TP sheet后反标过来</t>
         </is>
       </c>
-      <c r="C27" s="12" t="n"/>
-      <c r="D27" s="12" t="n"/>
-      <c r="E27" s="13" t="n"/>
+      <c r="C27" s="14" t="n"/>
+      <c r="D27" s="14" t="n"/>
+      <c r="E27" s="15" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="0" t="n"/>
@@ -1347,59 +1347,59 @@
   <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col width="12.375" customWidth="1" style="20" min="1" max="1"/>
-    <col width="13.5" customWidth="1" style="20" min="2" max="2"/>
-    <col width="12.625" customWidth="1" style="20" min="3" max="3"/>
-    <col width="68.75" customWidth="1" style="20" min="4" max="4"/>
-    <col width="13.875" customWidth="1" style="20" min="5" max="5"/>
-    <col width="15.75" customWidth="1" style="20" min="6" max="6"/>
+    <col width="12.375" customWidth="1" style="22" min="1" max="1"/>
+    <col width="13.5" customWidth="1" style="22" min="2" max="2"/>
+    <col width="12.625" customWidth="1" style="22" min="3" max="3"/>
+    <col width="68.75" customWidth="1" style="22" min="4" max="4"/>
+    <col width="13.875" customWidth="1" style="22" min="5" max="5"/>
+    <col width="15.75" customWidth="1" style="22" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26.1" customHeight="1" s="20">
+    <row r="1" ht="26.1" customHeight="1" s="22">
       <c r="A1" s="26" t="inlineStr">
         <is>
           <t>TestPoint分解表格</t>
         </is>
       </c>
-      <c r="B1" s="12" t="n"/>
-      <c r="C1" s="12" t="n"/>
-      <c r="D1" s="12" t="n"/>
-      <c r="E1" s="12" t="n"/>
-      <c r="F1" s="13" t="n"/>
-    </row>
-    <row r="2" ht="29.1" customHeight="1" s="20">
-      <c r="A2" s="11" t="inlineStr">
+      <c r="B1" s="14" t="n"/>
+      <c r="C1" s="14" t="n"/>
+      <c r="D1" s="14" t="n"/>
+      <c r="E1" s="14" t="n"/>
+      <c r="F1" s="15" t="n"/>
+    </row>
+    <row r="2" ht="29.1" customHeight="1" s="22">
+      <c r="A2" s="13" t="inlineStr">
         <is>
           <t>Feature编号</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
+      <c r="B2" s="13" t="inlineStr">
         <is>
           <t>TP类别</t>
         </is>
       </c>
-      <c r="C2" s="11" t="inlineStr">
+      <c r="C2" s="13" t="inlineStr">
         <is>
           <t>TP编号</t>
         </is>
       </c>
-      <c r="D2" s="11" t="inlineStr">
+      <c r="D2" s="13" t="inlineStr">
         <is>
           <t>TP描述</t>
         </is>
       </c>
-      <c r="E2" s="11" t="inlineStr">
+      <c r="E2" s="13" t="inlineStr">
         <is>
           <t>checker编号</t>
         </is>
       </c>
-      <c r="F2" s="11" t="inlineStr">
+      <c r="F2" s="13" t="inlineStr">
         <is>
           <t>Testcase编号</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="189" customHeight="1" s="20">
+    <row r="3" ht="189" customHeight="1" s="22">
       <c r="A3" s="7" t="inlineStr">
         <is>
           <t>FL_001_001</t>
@@ -1437,11 +1437,11 @@
       </c>
       <c r="F3" s="7" t="inlineStr">
         <is>
-          <t>DV_TC_001</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="202.5" customHeight="1" s="20">
+          <t>TC_001, TC_002</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="202.5" customHeight="1" s="22">
       <c r="A4" s="7" t="inlineStr">
         <is>
           <t>FL_002_001</t>
@@ -1474,16 +1474,16 @@
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>CHK_002</t>
+          <t>CHK_001</t>
         </is>
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>DV_TC_002, DV_TC_003</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="297" customHeight="1" s="20">
+          <t>TC_003, TC_004, TC_005</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="297" customHeight="1" s="22">
       <c r="A5" s="7" t="inlineStr">
         <is>
           <t>FL_003_001</t>
@@ -1520,16 +1520,16 @@
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>CHK_003</t>
+          <t>CHK_002</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>DV_TC_004, DV_TC_005, DV_TC_006</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="216" customHeight="1" s="20">
+          <t>TC_006, TC_007, TC_008, TC_009</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="216" customHeight="1" s="22">
       <c r="A6" s="7" t="inlineStr">
         <is>
           <t>FL_004_001</t>
@@ -1564,16 +1564,16 @@
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>CHK_004</t>
+          <t>CHK_003</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>DV_TC_007, DV_TC_008, DV_TC_009</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="216" customHeight="1" s="20">
+          <t>TC_010, TC_011, TC_012</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="216" customHeight="1" s="22">
       <c r="A7" s="7" t="inlineStr">
         <is>
           <t>FL_004_002</t>
@@ -1607,16 +1607,16 @@
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>CHK_005</t>
+          <t>CHK_004</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>DV_TC_010, DV_TC_011, DV_TC_012</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="243" customHeight="1" s="20">
+          <t>TC_013, TC_014, TC_015</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="243" customHeight="1" s="22">
       <c r="A8" s="7" t="inlineStr">
         <is>
           <t>FL_005_001</t>
@@ -1652,16 +1652,16 @@
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>CHK_006</t>
+          <t>CHK_005</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>DV_TC_013, DV_TC_014, DV_TC_015</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="243" customHeight="1" s="20">
+          <t>TC_016, TC_017, TC_018</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="243" customHeight="1" s="22">
       <c r="A9" s="7" t="inlineStr">
         <is>
           <t>FL_005_002</t>
@@ -1698,16 +1698,16 @@
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>CHK_007</t>
+          <t>CHK_006</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>DV_TC_016, DV_TC_017</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="229.5" customHeight="1" s="20">
+          <t>TC_019, TC_020, TC_021</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="229.5" customHeight="1" s="22">
       <c r="A10" s="7" t="inlineStr">
         <is>
           <t>FL_006_001</t>
@@ -1742,16 +1742,16 @@
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>CHK_008</t>
+          <t>CHK_007</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>DV_TC_018, DV_TC_019, DV_TC_020</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="256.5" customHeight="1" s="20">
+          <t>TC_022, TC_023, TC_024</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="256.5" customHeight="1" s="22">
       <c r="A11" s="7" t="inlineStr">
         <is>
           <t>FL_007_001</t>
@@ -1788,16 +1788,16 @@
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>CHK_009</t>
+          <t>CHK_008</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>DV_TC_021, DV_TC_022, DV_TC_023</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="175.5" customHeight="1" s="20">
+          <t>TC_025, TC_026, TC_027</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="175.5" customHeight="1" s="22">
       <c r="A12" s="7" t="inlineStr">
         <is>
           <t>FL_008_001</t>
@@ -1829,16 +1829,16 @@
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>CHK_010</t>
+          <t>CHK_009</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>DV_TC_024</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="283.5" customHeight="1" s="20">
+          <t>TC_028</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="283.5" customHeight="1" s="22">
       <c r="A13" s="7" t="inlineStr">
         <is>
           <t>FL_009_001</t>
@@ -1875,16 +1875,16 @@
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>CHK_011</t>
+          <t>CHK_010</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>DV_TC_025, DV_TC_026, DV_TC_027, DV_TC_028</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="202.5" customHeight="1" s="20">
+          <t>TC_029, TC_030, TC_031, TC_032, TC_033</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="202.5" customHeight="1" s="22">
       <c r="A14" s="7" t="inlineStr">
         <is>
           <t>FL_010_001</t>
@@ -1918,16 +1918,16 @@
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>CHK_012</t>
+          <t>CHK_011</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
-          <t>DV_TC_029, DV_TC_030</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="256.5" customHeight="1" s="20">
+          <t>TC_034, TC_035</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="256.5" customHeight="1" s="22">
       <c r="A15" s="7" t="inlineStr">
         <is>
           <t>FL_011_001</t>
@@ -1964,16 +1964,16 @@
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>CHK_013</t>
+          <t>CHK_012</t>
         </is>
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>DV_TC_031, DV_TC_032</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="216" customHeight="1" s="20">
+          <t>TC_036, TC_037, TC_038</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="216" customHeight="1" s="22">
       <c r="A16" s="7" t="inlineStr">
         <is>
           <t>FL_012_001</t>
@@ -2009,16 +2009,16 @@
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>CHK_014</t>
+          <t>CHK_013</t>
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
-          <t>DV_TC_033</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="162" customHeight="1" s="20">
+          <t>TC_039, TC_040</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="162" customHeight="1" s="22">
       <c r="A17" s="7" t="inlineStr">
         <is>
           <t>FL_013_001</t>
@@ -2050,16 +2050,16 @@
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>CHK_015</t>
+          <t>CHK_014</t>
         </is>
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>DV_TC_034, DV_TC_035</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="297" customHeight="1" s="20">
+          <t>TC_041</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="297" customHeight="1" s="22">
       <c r="A18" s="7" t="inlineStr">
         <is>
           <t>FL_014_001</t>
@@ -2098,35 +2098,35 @@
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>CHK_016</t>
+          <t>CHK_014</t>
         </is>
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
-          <t>DV_TC_036, DV_TC_037, DV_TC_038, DV_TC_039</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="24" customHeight="1" s="20">
-      <c r="A19" s="21" t="n"/>
-      <c r="B19" s="21" t="n"/>
-      <c r="C19" s="21" t="n"/>
+          <t>TC_042, TC_043, TC_044, TC_045</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="24" customHeight="1" s="22">
+      <c r="A19" s="23" t="n"/>
+      <c r="B19" s="23" t="n"/>
+      <c r="C19" s="23" t="n"/>
       <c r="D19" s="3" t="n"/>
-      <c r="E19" s="21" t="n"/>
-      <c r="F19" s="21" t="n"/>
+      <c r="E19" s="23" t="n"/>
+      <c r="F19" s="23" t="n"/>
     </row>
     <row r="20"/>
     <row r="21"/>
     <row r="22"/>
     <row r="23">
-      <c r="A23" s="19" t="inlineStr">
+      <c r="A23" s="21" t="inlineStr">
         <is>
           <t>填写说明</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="54.95" customHeight="1" s="20">
-      <c r="A24" s="21" t="inlineStr">
+    <row r="24" ht="54.95" customHeight="1" s="22">
+      <c r="A24" s="23" t="inlineStr">
         <is>
           <t>Feature编号</t>
         </is>
@@ -2138,13 +2138,13 @@
 3. Feature编号可以不是顺序的</t>
         </is>
       </c>
-      <c r="C24" s="12" t="n"/>
-      <c r="D24" s="12" t="n"/>
-      <c r="E24" s="12" t="n"/>
-      <c r="F24" s="13" t="n"/>
-    </row>
-    <row r="25" ht="71.09999999999999" customHeight="1" s="20">
-      <c r="A25" s="21" t="inlineStr">
+      <c r="C24" s="14" t="n"/>
+      <c r="D24" s="14" t="n"/>
+      <c r="E24" s="14" t="n"/>
+      <c r="F24" s="15" t="n"/>
+    </row>
+    <row r="25" ht="71.09999999999999" customHeight="1" s="22">
+      <c r="A25" s="23" t="inlineStr">
         <is>
           <t>TP类别</t>
         </is>
@@ -2158,13 +2158,13 @@
 </t>
         </is>
       </c>
-      <c r="C25" s="12" t="n"/>
-      <c r="D25" s="12" t="n"/>
-      <c r="E25" s="12" t="n"/>
-      <c r="F25" s="13" t="n"/>
-    </row>
-    <row r="26" ht="45.95" customHeight="1" s="20">
-      <c r="A26" s="21" t="inlineStr">
+      <c r="C25" s="14" t="n"/>
+      <c r="D25" s="14" t="n"/>
+      <c r="E25" s="14" t="n"/>
+      <c r="F25" s="15" t="n"/>
+    </row>
+    <row r="26" ht="45.95" customHeight="1" s="22">
+      <c r="A26" s="23" t="inlineStr">
         <is>
           <t>TP编号</t>
         </is>
@@ -2175,13 +2175,13 @@
 2. 允许TP编号没有对应的FL编号，即允许TP比FL多（例如’设备兼容性’这类TP）</t>
         </is>
       </c>
-      <c r="C26" s="12" t="n"/>
-      <c r="D26" s="12" t="n"/>
-      <c r="E26" s="12" t="n"/>
-      <c r="F26" s="13" t="n"/>
-    </row>
-    <row r="27" ht="38.1" customHeight="1" s="20">
-      <c r="A27" s="21" t="inlineStr">
+      <c r="C26" s="14" t="n"/>
+      <c r="D26" s="14" t="n"/>
+      <c r="E26" s="14" t="n"/>
+      <c r="F26" s="15" t="n"/>
+    </row>
+    <row r="27" ht="38.1" customHeight="1" s="22">
+      <c r="A27" s="23" t="inlineStr">
         <is>
           <t>Testcase编号</t>
         </is>
@@ -2191,13 +2191,13 @@
           <t xml:space="preserve"> 如果多个Testcase都可以cover同一个TP，写一个即可</t>
         </is>
       </c>
-      <c r="C27" s="12" t="n"/>
-      <c r="D27" s="12" t="n"/>
-      <c r="E27" s="12" t="n"/>
-      <c r="F27" s="13" t="n"/>
-    </row>
-    <row r="28" ht="41.1" customHeight="1" s="20">
-      <c r="A28" s="21" t="inlineStr">
+      <c r="C27" s="14" t="n"/>
+      <c r="D27" s="14" t="n"/>
+      <c r="E27" s="14" t="n"/>
+      <c r="F27" s="15" t="n"/>
+    </row>
+    <row r="28" ht="41.1" customHeight="1" s="22">
+      <c r="A28" s="23" t="inlineStr">
         <is>
           <t>Checker编号</t>
         </is>
@@ -2207,10 +2207,10 @@
           <t>可以重复</t>
         </is>
       </c>
-      <c r="C28" s="12" t="n"/>
-      <c r="D28" s="12" t="n"/>
-      <c r="E28" s="12" t="n"/>
-      <c r="F28" s="13" t="n"/>
+      <c r="C28" s="14" t="n"/>
+      <c r="D28" s="14" t="n"/>
+      <c r="E28" s="14" t="n"/>
+      <c r="F28" s="15" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -2235,10 +2235,10 @@
   <dimension ref="A1:D34"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col width="18.875" customWidth="1" style="20" min="1" max="1"/>
-    <col width="19.25" customWidth="1" style="20" min="2" max="2"/>
-    <col width="50.25" customWidth="1" style="20" min="3" max="3"/>
-    <col width="35.125" customWidth="1" style="20" min="4" max="4"/>
+    <col width="18.875" customWidth="1" style="22" min="1" max="1"/>
+    <col width="19.25" customWidth="1" style="22" min="2" max="2"/>
+    <col width="50.25" customWidth="1" style="22" min="3" max="3"/>
+    <col width="35.125" customWidth="1" style="22" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2247,48 +2247,51 @@
           <t>Checker List</t>
         </is>
       </c>
-      <c r="B1" s="12" t="n"/>
-      <c r="C1" s="12" t="n"/>
-      <c r="D1" s="13" t="n"/>
+      <c r="B1" s="14" t="n"/>
+      <c r="C1" s="14" t="n"/>
+      <c r="D1" s="15" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="11" t="inlineStr">
+      <c r="A2" s="13" t="inlineStr">
         <is>
           <t>CHK编号</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
+      <c r="B2" s="13" t="inlineStr">
         <is>
           <t>CHK Name</t>
         </is>
       </c>
-      <c r="C2" s="11" t="inlineStr">
+      <c r="C2" s="13" t="inlineStr">
         <is>
           <t>CHK描述</t>
         </is>
       </c>
-      <c r="D2" s="11" t="inlineStr">
+      <c r="D2" s="13" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="21" t="inlineStr">
+      <c r="A3" s="23" t="inlineStr">
         <is>
           <t>CHK_001</t>
         </is>
       </c>
-      <c r="B3" s="21" t="inlineStr">
-        <is>
-          <t>clk_stability_checker</t>
+      <c r="B3" s="23" t="inlineStr">
+        <is>
+          <t>clk_reset_checker</t>
         </is>
       </c>
       <c r="C3" s="7" t="inlineStr">
         <is>
-          <t>检查clk_i频率稳定性：
-1. 连续采样clk_i上升沿和下降沿计算实际频率，判断是否处于目标频率100MHz的允许误差范围内（±1%）
-2. 连续采样周期，对比相邻两个周期的频率偏差是否在3%内</t>
+          <t>检查时钟clk_i频率稳定性与rst_ni异步复位同步释放后模块状态正确性：
+1. clk_i目标频率100MHz，连续运行1000+周期频率偏差&lt;3%，无时钟毛刺或异常跳变；
+2. rst_ni异步复位（下降沿触发）：所有触发器立即清零，FSM强制进入IDLE/S_IDLE/AXI_IDLE态；
+3. rst_ni同步释放（与clk_i上升沿对齐）：释放后首个上升沿开始正常工作，无亚稳态；
+4. 复位后输出deassert：pdo_oe_o=0，htrans_o=2'b00(IDLE)，csr_rd_en_o=0，csr_wr_en_o=0，pdo_o[15:0]=16'b0；
+5. 复位后RX/TX上下文清空：协议状态清零，错误状态清零，CTRL.EN=0，CTRL.LANE_MODE=2'b00(1-bit默认)。</t>
         </is>
       </c>
       <c r="D3" s="3" t="n"/>
@@ -2301,15 +2304,16 @@
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>reset_state_checker</t>
+          <t>csr_access_checker</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>检查复位后状态：
-1. rst_ni拉低后，所有状态机（front_state、back_state）立即回到IDLE/S_IDLE
-2. 输出信号deassert：pdo_oe_o=0、htrans_o=2'b00(IDLE)、csr_rd_en_o=0、csr_wr_en_o=0
-3. pdo_o=4'b0（1-bit模式下pdo_o[0]=0），协议上下文清空</t>
+          <t>检查CSR接口读写时序正确性与地址范围合法性：
+1. CSR写操作：csr_wr_en_o为单周期脉冲，同一周期内csr_addr_o[7:0]与csr_wdata_o[31:0]有效，外部CSR File在该上升沿采样完成写入；
+2. CSR读操作：csr_rd_en_o为单周期脉冲，外部CSR File在下一周期将读数据稳定在csr_rdata_i[31:0]，模块在该周期采样（1 cycle读延迟）；
+3. CSR有效地址范围0x00~0x3F：reg_addr&gt;=0x40的访问在前置检查阶段即被拒绝，返回STS_BAD_REG(0x10)，不产生csr_rd_en_o/csr_wr_en_o脉冲；
+4. 寄存器属性正确：VERSION(0x00)为RO只读，CTRL(0x04)为RW读写，STATUS(0x08)为RO只读，LAST_ERR(0x0C)为RO只读，软件通过轮询STATUS获取状态。</t>
         </is>
       </c>
       <c r="D4" s="9" t="n"/>
@@ -2322,16 +2326,16 @@
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>csr_access_checker</t>
+          <t>test_mode_en_checker</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>检查CSR访问时序：
-1. WR_CSR：csr_wr_en_o脉冲持续1周期，同一周期采样csr_addr_o和csr_wdata_o
-2. RD_CSR：csr_rd_en_o脉冲后下一周期采样csr_rdata_i
-3. CSR有效地址范围：0x00 ~ 0x3F
-4. 地址越界（reg_addr &gt;= 0x40）：返回STS_BAD_REG(0x10)，不发起CSR访问</t>
+          <t>检查test_mode_i与en_i信号对命令的拒绝行为与错误优先级正确性：
+1. test_mode_i=0时：所有命令被前置检查拒绝，返回STS_NOT_IN_TEST(0x04)，不发起任何CSR/AHB访问（csr_wr_en_o=0，csr_rd_en_o=0，htrans_o=IDLE）；
+2. en_i=0时：所有命令被前置检查拒绝，返回STS_DISABLED(0x08)，不发起任何CSR/AHB访问；
+3. 错误优先级：当test_mode_i=0且en_i=0同时成立时，返回STS_NOT_IN_TEST(0x04)（优先级高于STS_DISABLED）；
+4. 检查时刻：test_mode_i与en_i在frame_valid时刻被前置检查器组合采样，帧接收期间不检查。</t>
         </is>
       </c>
       <c r="D5" s="9" t="n"/>
@@ -2344,15 +2348,16 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>test_mode_en_checker</t>
+          <t>lane_mode_checker</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>检查test_mode_i和en_i前置条件：
-1. test_mode_i=0时：所有命令返回STS_NOT_IN_TEST(0x04)，不发起CSR/AHB访问
-2. en_i=0时：所有命令返回STS_DISABLED(0x08)，不发起CSR/AHB访问
-3. 错误优先级：STS_NOT_IN_TEST(0x04) &gt; STS_DISABLED(0x08)</t>
+          <t>检查lane_mode_i对应的通道宽度与数据信号使用正确性（MVP仅支持1-bit与4-bit）：
+1. lane_mode_i=2'b00(1-bit模式)：仅使用pdi_i[0]/pdo_o[0]，pdi_i[15:1]忽略，pdo_o[15:1]驱动为0；RD_CSR帧16bit需16个周期接收；
+2. lane_mode_i=2'b01(4-bit模式)：使用pdi_i[3:0]/pdo_o[3:0]，按高nibble优先发送；RD_CSR帧16bit需4个周期接收；
+3. lane_mode_i在接收器(SLC_CAXIS)和发送器(SLC_SAXIS)中被连续组合采样，用于计算每拍移位宽度bpc(bits per clock)；
+4. 事务边界约束：lane_mode_i在pcs_n_i=0期间必须保持稳定，事务中途切换导致移位宽度变化、帧数据错位，可能触发STS_BAD_OPCODE或STS_FRAME_ERR。</t>
         </is>
       </c>
       <c r="D6" s="9" t="n"/>
@@ -2365,16 +2370,17 @@
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>lane_mode_checker</t>
+          <t>frame_protocol_checker</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>检查lane_mode配置和帧收发行为：
-1. lane_mode_i=2'b00时：仅使用pdi_i[0]/pdo_o[0]，RD_CSR命令16bit帧需16周期接收
-2. lane_mode_i=2'b01时：使用pdi_i[3:0]/pdo_o[3:0]，RD_CSR命令16bit帧需4周期接收
-3. MVP不支持：8/16-bit lane模式（lane_mode_i=2'b10/11）
-4. 事务执行期间（pcs_n_i=0）lane_mode_i必须保持稳定</t>
+          <t>检查pcs_n_i帧边界协议与pdo_oe_o方向控制正确性：
+1. 帧边界定义：pcs_n_i=1为空闲态，pcs_n_i下降沿开启一次事务（帧接收→执行→响应发送），pcs_n_i上升沿结束事务；
+2. 请求阶段：pcs_n_i=0期间ATE驱动pdi_i输入数据，模块接收移位锁存；
+3. Turnaround：请求与响应之间固定插入1个clk_i周期，pdo_oe_o=0保持高阻态，避免总线冲突；
+4. 响应阶段：pdo_oe_o=1表示模块驱动pdo_o输出，响应帧按MSB-first顺序串行发送；
+5. 帧中止行为：若pcs_n_i在接收中途提前拉高且opcode已锁存，产生frame_abort，返回STS_FRAME_ERR(0x01)。</t>
         </is>
       </c>
       <c r="D7" s="9" t="n"/>
@@ -2387,15 +2393,23 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>frame_protocol_checker</t>
+          <t>frame_length_checker</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>检查帧协议：
-1. pcs_n_i=0期间接收数据，turnaround后pdo_oe_o=1驱动响应
-2. 帧中止（pcs_n_i提前拉高）：返回STS_FRAME_ERR(0x01)
-3. 帧长度检查：WR_CSR 48bit、RD_CSR 16bit、AHB_WR32 72bit、AHB_RD32 40bit</t>
+          <t>检查各类命令帧长度与响应帧长度符合协议规范：
+1. 命令帧长度（MSB-first）：
+   - WR_CSR(opcode=0x10)：48-bit = opcode(8) + reg_addr(8) + wdata(32)
+   - RD_CSR(opcode=0x11)：16-bit = opcode(8) + reg_addr(8)
+   - AHB_WR32(opcode=0x20)：72-bit = opcode(8) + addr(32) + wdata(32)
+   - AHB_RD32(opcode=0x21)：40-bit = opcode(8) + addr(32)
+2. 响应帧长度：
+   - 写命令响应：8-bit status_code
+   - 读命令响应：40-bit = status(8) + rdata(32)
+3. 各lane_mode下的接收周期数：
+   - 1-bit模式：WR_CSR需48周期，RD_CSR需16周期
+   - 4-bit模式：WR_CSR需12周期，RD_CSR需4周期。</t>
         </is>
       </c>
       <c r="D8" s="9" t="n"/>
@@ -2408,15 +2422,19 @@
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>response_frame_checker</t>
+          <t>opcode_decode_checker</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>检查响应帧格式：
-1. 写命令响应：8bit status_code
-2. 读命令响应：40bit（status 8bit + rdata 32bit）
-3. turnaround固定1周期</t>
+          <t>检查opcode译码正确性与非法opcode检测：
+1. 有效opcode译码（帧接收满8bit后锁存opcode_latched_q）：
+   - 0x10译码为WR_CSR：CSR写路径，发起csr_wr_en_o脉冲
+   - 0x11译码为RD_CSR：CSR读路径，发起csr_rd_en_o脉冲
+   - 0x20译码为AHB_WR32：AHB单次写，发起htrans=NONSEQ+hwrite=1
+   - 0x21译码为AHB_RD32：AHB单次读，发起htrans=NONSEQ+hwrite=0
+2. 非法opcode检测：opcode不在{0x10, 0x11, 0x20, 0x21}中时，前置检查返回STS_BAD_OPCODE(0x02)；
+3. 错误优先级：STS_BAD_OPCODE(0x02)优先级低于STS_FRAME_ERR(0x01)，高于STS_NOT_IN_TEST(0x04)。</t>
         </is>
       </c>
       <c r="D9" s="9" t="n"/>
@@ -2429,15 +2447,17 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>opcode_decode_checker</t>
+          <t>ctrl_register_checker</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>检查opcode译码：
-1. 有效opcode：0x10→WR_CSR、0x11→RD_CSR、0x20→AHB_WR32、0x21→AHB_RD32
-2. 非法opcode（不在0x10/0x11/0x20/0x21中）：返回STS_BAD_OPCODE(0x02)，不发起任何访问
-3. MVP不支持：Burst命令（0x22/0x23）</t>
+          <t>检查CTRL寄存器配置生效与lane_mode切换约束：
+1. CTRL.EN(bit0)：写1使能模块功能，写0禁用（等同于en_i=0效果，但通过命令配置）；
+2. CTRL.LANE_MODE(bit[2:1])：写入00/01配置lane模式，镜像lane_mode_i端口值；
+3. CTRL.SOFT_RST(bit3)：写1触发协议上下文软复位，清空RX/TX状态，恢复LANE_MODE为默认值(1-bit)；
+4. 配置生效时机：WR_CSR命令执行后配置立即生效，下一帧接收使用新配置；
+5. 事务期间lane_mode稳定：lane_mode_i在pcs_n_i=0期间不得切换，否则导致帧数据损坏（模块不检测此违规）。</t>
         </is>
       </c>
       <c r="D10" s="9" t="n"/>
@@ -2450,15 +2470,21 @@
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>ctrl_reg_config_checker</t>
+          <t>status_report_checker</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>检查CTRL寄存器配置：
-1. LANE_MODE切换：MVP仅允许00=1-bit、01=4-bit
-2. SOFT_RST=1：协议上下文清零，lane模式恢复默认（1-bit）
-3. 事务期间lane_mode_i切换：帧数据错位（模块不检测此违规）</t>
+          <t>检查STATUS寄存器与LAST_ERR寄存器的状态报告正确性：
+1. STATUS[0](BUSY)：当前有事务执行时为1，空闲时为0；
+2. STATUS[1](RESP_VALID)：最近响应有效时为1；
+3. STATUS[2](CMD_ERR)：命令错误sticky位，有错误发生时置1，软件写1清零；
+4. STATUS[3](BUS_ERR)：总线错误sticky位，AHB错误时置1；
+5. STATUS[4](FRAME_ERR)：帧错误sticky位；
+6. STATUS[5](IN_TEST_MODE)：镜像test_mode_i端口值；
+7. STATUS[6](OUT_EN)：镜像pdo_oe_o信号；
+8. LAST_ERR[7:0]：存储最近一次错误的状态码，新命令开始后被覆盖；
+9. MVP版本无独立中断输出：所有状态通过寄存器轮询获取。</t>
         </is>
       </c>
       <c r="D11" s="9" t="n"/>
@@ -2471,15 +2497,18 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>status_reg_checker</t>
+          <t>error_priority_checker</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>检查STATUS和LAST_ERR寄存器：
-1. MVP版本无独立中断输出端口
-2. STATUS位域：BUSY[0]/RESP_VALID[1]/CMD_ERR[2]/BUS_ERR[3]/FRAME_ERR[4]/IN_TEST_MODE[5]/OUT_EN[6]
-3. LAST_ERR存储最近错误码</t>
+          <t>检查错误优先级链与执行期错误检测正确性：
+1. 前置检查错误按固定优先级链返回（高→低）：
+   STS_FRAME_ERR(0x01) &gt; STS_BAD_OPCODE(0x02) &gt; STS_NOT_IN_TEST(0x04) &gt; STS_DISABLED(0x08) &gt; STS_BAD_REG(0x10) &gt; STS_ALIGN_ERR(0x20)；
+2. 任何前置错误均在发起CSR/AHB访问前收敛，不产生csr_wr_en_o/csr_rd_en_o/htrans_o脉冲；
+3. STS_AHB_ERR(0x40)不在前置优先级链中：仅在前置检查全部通过后、AHB事务实际执行期间发生，与前置错误互斥；
+4. AHB执行期错误：hresp_i=1时返回STS_AHB_ERR(0x40)；hready_i持续为0超过BUS_TIMEOUT_CYCLES(256)周期触发超时，返回STS_AHB_ERR(0x40)；
+5. 多错误并发：仅报告最高优先级错误，不累积多错误。</t>
         </is>
       </c>
       <c r="D12" s="9" t="n"/>
@@ -2492,15 +2521,17 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>error_priority_checker</t>
+          <t>low_power_checker</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>检查错误优先级链：
-1. 前置错误优先级：STS_FRAME_ERR(0x01) &gt; STS_BAD_OPCODE(0x02) &gt; STS_NOT_IN_TEST(0x04) &gt; STS_DISABLED(0x08) &gt; STS_BAD_REG(0x10) &gt; STS_ALIGN_ERR(0x20)
-2. 执行期错误STS_AHB_ERR(0x40)：hresp_i=1或超时（256周期）
-3. 多个前置错误同时成立时，仅报告最高优先级错误</t>
+          <t>检查空闲态低功耗行为与门控条件正确性：
+1. pcs_n_i=1空闲态：接收移位寄存器(rx_shift_q)不更新，发送移位寄存器(tx_shift_q)不翻转；
+2. 超时计数器：仅在AXI_WAIT状态工作，其他状态不计数不翻转；
+3. test_mode_i=0时：AHB输出保持空闲（htrans_o=2'b00 IDLE，hburst_o=3'b000 SINGLE，haddr_o=0）；
+4. 门控时钟条件：RX移位逻辑门控条件为pcs_n_i=1，TX移位逻辑门控条件为非TX态，超时计数器门控条件为state!=AXI_WAIT；
+5. 空闲态触发器翻转率目标：&lt;工作态的5%。</t>
         </is>
       </c>
       <c r="D13" s="9" t="n"/>
@@ -2513,15 +2544,19 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>low_power_checker</t>
+          <t>performance_checker</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>检查低功耗行为：
-1. 空闲态（pcs_n_i=1）：接收/发送移位寄存器不更新，超时计数器不工作
-2. test_mode_i=0：AHB输出保持IDLE（htrans_o=2'b00）
-3. 仅在RX/TX/WAIT_AHB状态翻转关键寄存器</t>
+          <t>检查端到端延时符合预期与地址对齐检查：
+1. 4-bit模式延时估计：
+   - AHB_RD32：RX(10周期)+译码(2)+AHB(2)+TA(1)+TX(10)≈23~24周期
+   - AHB_WR32：RX(18)+译码(2)+AHB(2)+TA(1)+TX(2)≈23周期
+   - WR_CSR：RX(12)+执行(1)+TA(1)+TX(2)≈16周期
+2. 1-bit模式延时：约为4-bit的4倍（因帧长×4）
+3. 地址对齐检查：AHB命令addr[1:0]!=2'b00返回STS_ALIGN_ERR(0x20)，对齐地址正常发起AHB访问；
+4. hsize_o固定3'b010(WORD)，hburst_o固定3'b000(SINGLE)。</t>
         </is>
       </c>
       <c r="D14" s="9" t="n"/>
@@ -2534,16 +2569,17 @@
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>performance_checker</t>
+          <t>dfx_observability_checker</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>检查性能指标：
-1. 目标频率：100MHz
-2. 地址对齐检查：addr[1:0]=2'b00，非对齐返回STS_ALIGN_ERR(0x20)，不发起AHB访问
-3. 1-bit模式原始线速：12.5 MB/s
-4. 4-bit模式原始线速：50 MB/s</t>
+          <t>检查内部调试观测点可正确反映状态：
+1. FSM状态观测：front_state_q(IDLE/ISSUE/WAIT_RESP/TA/TX)、back_state_q、axi_state_q(AXI_IDLE/AXI_REQ/AXI_WAIT/AXI_DONE/AXI_ERR)；
+2. 命令信息观测：opcode_latched_q[7:0]、burst_len、addr暂存值、wdata暂存值、rdata暂存值；
+3. 状态码观测：status_code[7:0]、错误优先级判定结果；
+4. 计数器观测：rx_count_q、tx_count_q、timeout_cnt；
+5. 观测用途：仿真通过XMR直接观察，硅后通过DFT扫描链抽出或外部CSR镜像。</t>
         </is>
       </c>
       <c r="D15" s="9" t="n"/>
@@ -2556,63 +2592,34 @@
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>dfx_observability_checker</t>
+          <t>ahb_master_checker</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>检查DFX可观测点：
-1. front_state/back_state状态机状态
-2. opcode_latched_q锁存值
-3. addr/wdata/rdata暂存值
-4. status_code错误码
-5. rx_count/tx_count计数器</t>
+          <t>检查AHB-Lite Master协议符合性与2-phase流水正确性：
+1. 2-phase流水：
+   - T1地址相：驱动haddr_o[31:0]、hwrite_o、htrans_o=2'b10(NONSEQ)、hsize_o=3'b010、hburst_o=3'b000
+   - T2数据相：写操作驱动hwdata_o[31:0]，读操作采样hrdata_i[31:0]
+   - haddr与hwdata/hrdata必然错开1拍
+2. 固定参数：hsize_o=3'b010(WORD)、hburst_o=3'b000(SINGLE)，不支持byte/halfword/Burst；
+3. AHB错误响应：hresp_i=1时FSM进入AXI_ERR，返回STS_AHB_ERR(0x40)，AHB输出恢复IDLE；
+4. 超时检测：hready_i=0持续256周期触发超时，进入AXI_ERR；
+5. CSR不进入AHB memory map：CSR通过WR_CSR/RD_CSR命令访问，不产生AHB事务。</t>
         </is>
       </c>
       <c r="D16" s="9" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="8" t="inlineStr">
-        <is>
-          <t>CHK_015</t>
-        </is>
-      </c>
-      <c r="B17" s="8" t="inlineStr">
-        <is>
-          <t>memory_map_checker</t>
-        </is>
-      </c>
-      <c r="C17" s="7" t="inlineStr">
-        <is>
-          <t>检查Memory map：
-1. 模块CSR不进入SoC AHB memory map
-2. CSR仅通过协议命令访问（opcode=0x10/0x11）
-3. AHB Master访问使用32bit地址、word访问粒度</t>
-        </is>
-      </c>
+      <c r="A17" s="8" t="n"/>
+      <c r="B17" s="8" t="n"/>
+      <c r="C17" s="7" t="n"/>
       <c r="D17" s="9" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="inlineStr">
-        <is>
-          <t>CHK_016</t>
-        </is>
-      </c>
-      <c r="B18" s="8" t="inlineStr">
-        <is>
-          <t>ahb_protocol_checker</t>
-        </is>
-      </c>
-      <c r="C18" s="7" t="inlineStr">
-        <is>
-          <t>检查AHB-Lite协议：
-1. 2-phase流水：T1地址相驱动haddr+hwrite+htrans=NONSEQ(2'b10)，T2数据相驱动hwdata或采样hrdata
-2. 固定参数：hsize_o=3'b010(WORD)、hburst_o=3'b000(SINGLE)
-3. 地址必须4-byte对齐（addr[1:0]=2'b00）
-4. hresp_i=1返回STS_AHB_ERR(0x40)
-5. MVP仅支持Single事务，不支持Burst</t>
-        </is>
-      </c>
+      <c r="A18" s="8" t="n"/>
+      <c r="B18" s="8" t="n"/>
+      <c r="C18" s="7" t="n"/>
       <c r="D18" s="9" t="n"/>
     </row>
     <row r="19">
@@ -2664,14 +2671,14 @@
       <c r="D26" s="9" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="19" t="inlineStr">
+      <c r="A30" s="21" t="inlineStr">
         <is>
           <t>填写要求</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="24" customHeight="1" s="20">
-      <c r="A31" s="21" t="inlineStr">
+    <row r="31" ht="24" customHeight="1" s="22">
+      <c r="A31" s="23" t="inlineStr">
         <is>
           <t>CHK Name</t>
         </is>
@@ -2681,11 +2688,11 @@
           <t>如果是SVA checker，需填写SVA property名字</t>
         </is>
       </c>
-      <c r="C31" s="12" t="n"/>
-      <c r="D31" s="13" t="n"/>
-    </row>
-    <row r="32" ht="69.95" customHeight="1" s="20">
-      <c r="A32" s="21" t="inlineStr">
+      <c r="C31" s="14" t="n"/>
+      <c r="D31" s="15" t="n"/>
+    </row>
+    <row r="32" ht="69.95" customHeight="1" s="22">
+      <c r="A32" s="23" t="inlineStr">
         <is>
           <t>CHK描述</t>
         </is>
@@ -2697,20 +2704,20 @@
 </t>
         </is>
       </c>
-      <c r="C32" s="12" t="n"/>
-      <c r="D32" s="13" t="n"/>
+      <c r="C32" s="14" t="n"/>
+      <c r="D32" s="15" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="21" t="n"/>
+      <c r="A33" s="23" t="n"/>
       <c r="B33" s="8" t="n"/>
-      <c r="C33" s="12" t="n"/>
-      <c r="D33" s="13" t="n"/>
+      <c r="C33" s="14" t="n"/>
+      <c r="D33" s="15" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="21" t="n"/>
+      <c r="A34" s="23" t="n"/>
       <c r="B34" s="8" t="n"/>
-      <c r="C34" s="12" t="n"/>
-      <c r="D34" s="13" t="n"/>
+      <c r="C34" s="14" t="n"/>
+      <c r="D34" s="15" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -2734,10 +2741,10 @@
   <dimension ref="A1:D65"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col width="13.75" customWidth="1" style="20" min="1" max="1"/>
-    <col width="20" customWidth="1" style="20" min="2" max="2"/>
-    <col width="53.5" customWidth="1" style="25" min="3" max="3"/>
-    <col width="14.25" customWidth="1" style="20" min="4" max="4"/>
+    <col width="13.75" customWidth="1" style="22" min="1" max="1"/>
+    <col width="20" customWidth="1" style="22" min="2" max="2"/>
+    <col width="53.5" customWidth="1" style="12" min="3" max="3"/>
+    <col width="14.25" customWidth="1" style="22" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2746,27 +2753,27 @@
           <t>Test Case List</t>
         </is>
       </c>
-      <c r="B1" s="12" t="n"/>
-      <c r="C1" s="12" t="n"/>
-      <c r="D1" s="13" t="n"/>
+      <c r="B1" s="14" t="n"/>
+      <c r="C1" s="14" t="n"/>
+      <c r="D1" s="15" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="11" t="inlineStr">
+      <c r="A2" s="13" t="inlineStr">
         <is>
           <t>TC编号</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
+      <c r="B2" s="13" t="inlineStr">
         <is>
           <t>TC Name</t>
         </is>
       </c>
-      <c r="C2" s="11" t="inlineStr">
+      <c r="C2" s="13" t="inlineStr">
         <is>
           <t>TC 描述</t>
         </is>
       </c>
-      <c r="D2" s="11" t="inlineStr">
+      <c r="D2" s="13" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
@@ -2775,27 +2782,29 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>DV_TC_001</t>
+          <t>TC_001</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>clk_100mhz_stability_test</t>
-        </is>
-      </c>
-      <c r="C3" s="24" t="inlineStr">
+          <t>test_clock_stability</t>
+        </is>
+      </c>
+      <c r="C3" s="11" t="inlineStr">
         <is>
           <t>配置条件：
-1. 模块上电复位完成，test_mode_i=1，en_i=1
-2. 系统时钟clk_i配置为100MHz目标频率
-3. 配置LANE_MODE=01（4-bit模式）
+1.模块上电复位完成，clk_i配置为100MHz目标频率；
+2.test_mode_i=1，en_i=1，lane_mode_i=2'b01（4-bit模式）；
 输入激励：
-1. 持续运行模块超过1000个时钟周期
-2. 通过ATE接口发送多条RD_CSR命令（opcode=0x11）读取VERSION寄存器（reg_addr=0x00）
+1.持续运行模块超过1000个时钟周期，观察clk_i波形稳定性；
+2.通过ATE接口连续发送10条RD_CSR命令（opcode=0x11，reg_addr=0x00读取VERSION寄存器）；
+3.记录每条命令的响应周期数和status_code；
+4.在不同lane_mode下（1-bit和4-bit）重复测试；
 期望结果：
-1. 时钟稳定性满足要求，连续采样周期频率偏差&lt;3%
-2. 所有命令响应status_code=STS_OK(0x00)
-3. 无时钟相关的协议错误或超时
+1.时钟波形稳定，无毛刺或异常跳变，周期偏差&lt;3%；
+2.所有RD_CSR命令响应正常，status_code=STS_OK(0x00)；
+3.rdata返回VERSION寄存器固定值；
+4.无时钟相关的协议错误或超时；
 coverage check点：
 直接用例覆盖，不收功能覆盖率</t>
         </is>
@@ -2805,27 +2814,29 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>DV_TC_002</t>
+          <t>TC_002</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>async_reset_test</t>
-        </is>
-      </c>
-      <c r="C4" s="24" t="inlineStr">
+          <t>test_clock_frequency</t>
+        </is>
+      </c>
+      <c r="C4" s="11" t="inlineStr">
         <is>
           <t>配置条件：
-1. 模块上电，clk_i稳定运行
-2. 初始配置test_mode_i=1，en_i=1，lane_mode_i=2'b01
+1.模块上电复位完成，clk_i运行；
+2.test_mode_i=1，en_i=1；
 输入激励：
-1. 拉低rst_ni触发异步复位（至少持续2个clk_i周期）
-2. 释放rst_ni（同步释放）
-3. 检查复位后状态：front_state=IDLE，back_state=S_IDLE，pdo_oe_o=0，htrans_o=2'b00
+1.配置lane_mode_i=2'b00（1-bit模式）；
+2.发送RD_CSR命令测量帧接收时间，计算等效周期数；
+3.配置lane_mode_i=2'b01（4-bit模式）；
+4.发送RD_CSR命令测量帧接收时间，验证周期数为1-bit的1/4；
+5.多次测量取平均值；
 期望结果：
-1. 复位后所有状态机回到IDLE态
-2. 输出信号deassert：pdo_oe_o=0，htrans_o=IDLE，csr_rd_en_o=0，csr_wr_en_o=0
-3. pdo_o=4'b0，协议上下文清空
+1.1-bit模式下RD_CSR帧(16bit)需16周期接收；
+2.4-bit模式下RD_CSR帧(16bit)需4周期接收；
+3.频率偏差&lt;3%，无异常；
 coverage check点：
 直接用例覆盖，不收功能覆盖率</t>
         </is>
@@ -2835,26 +2846,29 @@
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>DV_TC_003</t>
+          <t>TC_003</t>
         </is>
       </c>
       <c r="B5" s="10" t="inlineStr">
         <is>
-          <t>reset_during_operation_test</t>
-        </is>
-      </c>
-      <c r="C5" s="24" t="inlineStr">
+          <t>test_reset_behavior</t>
+        </is>
+      </c>
+      <c r="C5" s="11" t="inlineStr">
         <is>
           <t>配置条件：
-1. 模块复位完成，test_mode_i=1，en_i=1，lane_mode_i=2'b01
+1.模块上电，clk_i稳定运行100MHz；
+2.初始配置test_mode_i=1，en_i=1，lane_mode_i=2'b01（4-bit模式）；
 输入激励：
-1. 发送RD_CSR命令（opcode=0x11, reg_addr=0x00）
-2. 在接收中途（pdi_i已发送8bit后）拉低rst_ni
-3. 释放rst_ni后检查状态机状态
+1.拉低rst_ni触发异步复位，持续至少2个clk_i周期；
+2.释放rst_ni（同步释放，与clk_i上升沿对齐）；
+3.检查复位后状态：读取STATUS寄存器验证BUSY=0；
+4.发送RD_CSR命令（opcode=0x11，reg_addr=0x00）验证模块恢复工作；
 期望结果：
-1. 状态机强制回到IDLE/S_IDLE
-2. pdo_oe_o=0
-3. htrans_o=2'b00(IDLE)
+1.复位后所有状态机回到IDLE态：front_state=IDLE，back_state=S_IDLE，axi_state=AXI_IDLE；
+2.输出信号deassert：pdo_oe_o=0，htrans_o=2'b00(IDLE)，csr_rd_en_o=0，csr_wr_en_o=0；
+3.pdo_o[15:0]=16'b0，协议上下文清空；
+4.复位释放后RD_CSR命令正常响应status_code=STS_OK(0x00)；
 coverage check点：
 直接用例覆盖，不收功能覆盖率</t>
         </is>
@@ -2864,27 +2878,30 @@
     <row r="6">
       <c r="A6" s="10" t="inlineStr">
         <is>
-          <t>DV_TC_004</t>
+          <t>TC_004</t>
         </is>
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>csr_write_read_test</t>
-        </is>
-      </c>
-      <c r="C6" s="24" t="inlineStr">
+          <t>test_reset_recovery</t>
+        </is>
+      </c>
+      <c r="C6" s="11" t="inlineStr">
         <is>
           <t>配置条件：
-1. 模块复位完成，test_mode_i=1，en_i=1
-2. 配置LANE_MODE=01（4-bit模式）
+1.模块复位完成，test_mode_i=1，en_i=1；
+2.lane_mode_i=2'b01（4-bit模式）；
 输入激励：
-1. 发送WR_CSR命令：opcode=0x10，reg_addr=0x04(CTRL)，wdata=0x00000001（EN=1）
-2. 发送RD_CSR命令：opcode=0x11，reg_addr=0x00(VERSION)验证读返回
-3. 发送RD_CSR命令：opcode=0x11，reg_addr=0x08(STATUS)读取状态寄存器
+1.发送WR_CSR命令（opcode=0x10，reg_addr=0x04(CTRL)，wdata=0x00000001）配置CTRL.EN=1；
+2.发送RD_CSR命令（opcode=0x11，reg_addr=0x04）验证写入；
+3.触发复位：拉低rst_ni至少2周期后释放；
+4.复位后再次发送RD_CSR命令验证功能恢复；
+5.检查CTRL.EN复位后是否变为0；
 期望结果：
-1. WR_CSR：csr_wr_en_o脉冲1周期，同周期采样csr_addr_o/csr_wdata_o，响应status_code=STS_OK(0x00)
-2. RD_CSR VERSION：csr_rd_en_o脉冲后下一周期采样csr_rdata_i，响应status_code=STS_OK(0x00)+rdata
-3. RD_CSR STATUS：返回STATUS寄存器当前值
+1.WR_CSR执行成功，status_code=STS_OK(0x00)；
+2.RD_CSR读回CTRL=0x00000001；
+3.复位后CTRL.EN=0，LANE_MODE=2'b00（默认值）；
+4.复位释放后模块接受新命令并正常响应；
 coverage check点：
 直接用例覆盖，不收功能覆盖率</t>
         </is>
@@ -2894,27 +2911,29 @@
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
         <is>
-          <t>DV_TC_005</t>
+          <t>TC_005</t>
         </is>
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>csr_addr_boundary_test</t>
-        </is>
-      </c>
-      <c r="C7" s="24" t="inlineStr">
+          <t>test_reset_during_transaction</t>
+        </is>
+      </c>
+      <c r="C7" s="11" t="inlineStr">
         <is>
           <t>配置条件：
-1. 模块复位完成，test_mode_i=1，en_i=1
-2. 配置LANE_MODE=01（4-bit模式）
+1.模块复位完成，test_mode_i=1，en_i=1；
+2.lane_mode_i=2'b01（4-bit模式）；
 输入激励：
-1. 发送RD_CSR命令：opcode=0x11，reg_addr=0x40（超出0x00~0x3F范围）
-2. 发送RD_CSR命令：opcode=0x11，reg_addr=0xFF（最大非法地址）
-3. 发送WR_CSR命令：opcode=0x10，reg_addr=0x3F（有效地址上界），wdata=0xDEADBEEF
+1.开始发送AHB_WR32命令（opcode=0x20，addr=0x10000000，wdata=0xDEADBEEF）；
+2.在帧接收中途（如收到24bit后）触发rst_ni复位；
+3.释放复位后检查状态机状态和输出；
+4.发送新的RD_CSR命令验证恢复；
 期望结果：
-1. reg_addr=0x40：返回STS_BAD_REG(0x10)，不发起CSR访问
-2. reg_addr=0xFF：返回STS_BAD_REG(0x10)，不发起CSR访问
-3. reg_addr=0x3F：正常访问，status_code=STS_OK(0x00)
+1.复位立即生效，FSM强制回到IDLE态；
+2.输出deassert：pdo_oe_o=0，htrans_o=IDLE；
+3.事务中止，不产生AHB访问；
+4.复位释放后新命令正常响应；
 coverage check点：
 直接用例覆盖，不收功能覆盖率</t>
         </is>
@@ -2924,29 +2943,30 @@
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>DV_TC_006</t>
+          <t>TC_006</t>
         </is>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>csr_random_access_test</t>
-        </is>
-      </c>
-      <c r="C8" s="24" t="inlineStr">
+          <t>test_csr_write</t>
+        </is>
+      </c>
+      <c r="C8" s="11" t="inlineStr">
         <is>
           <t>配置条件：
-1. 模块复位完成，test_mode_i=1，en_i=1
-2. 随机配置lane_mode_i（2'b00/01）
+1.模块复位完成，test_mode_i=1，en_i=1；
+2.lane_mode_i=2'b01（4-bit模式）；
 输入激励：
-1. 随机选择WR_CSR(opcode=0x10)或RD_CSR(opcode=0x11)命令
-2. 随机生成reg_addr：有效范围0x00~0x3F，或无效范围&gt;=0x40
-3. 对WR_CSR随机生成wdata
-4. 重复执行N次（N≥10），每次随机配置
+1.发送WR_CSR命令（opcode=0x10，reg_addr=0x04(CTRL)，wdata=0x00000001）写入CTRL.EN=1；
+2.观察csr_wr_en_o脉冲时序：单周期脉冲，同周期采样csr_addr_o=0x04、csr_wdata_o=0x01；
+3.发送RD_CSR命令（opcode=0x11，reg_addr=0x04）读回验证写入；
+4.写VERSION寄存器（reg_addr=0x00，RO）：发送WR_CSR命令验证写被忽略；
 期望结果：
-1. 有效地址(reg_addr&lt;0x40)：返回status=STS_OK(0x00)
-2. 无效地址(reg_addr&gt;=0x40)：返回STS_BAD_REG(0x10)，不发起CSR访问
+1.WR_CSR执行成功：csr_wr_en_o脉冲持续1周期，响应status_code=STS_OK(0x00)；
+2.RD_CSR读回CTRL=0x00000001，验证写入生效；
+3.写VERSION(RO)寄存器不改变其值，响应status_code=STS_OK(0x00)；
 coverage check点：
-覆盖所有CSR地址范围（0x00/0x04/0x08/0x0C），覆盖lane_mode=2'b00和2'b01</t>
+对CSR地址范围0x00~0x03采集功能覆盖率</t>
         </is>
       </c>
       <c r="D8" s="9" t="n"/>
@@ -2954,1187 +2974,1463 @@
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>DV_TC_007</t>
+          <t>TC_007</t>
         </is>
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>test_mode_reject_test</t>
-        </is>
-      </c>
-      <c r="C9" s="24" t="inlineStr">
+          <t>test_csr_read</t>
+        </is>
+      </c>
+      <c r="C9" s="11" t="inlineStr">
         <is>
           <t>配置条件：
-1. 模块复位完成，lane_mode_i=2'b01（4-bit）
+1.模块复位完成，test_mode_i=1，en_i=1；
+2.lane_mode_i=2'b01（4-bit模式）；
 输入激励：
-1. 设置test_mode_i=0，en_i=1
-2. 发送RD_CSR命令：opcode=0x11，reg_addr=0x00
-3. 检查响应帧status_code
-4. 再设置test_mode_i=1，发送同一命令验证恢复正常
+1.发送RD_CSR命令（opcode=0x11，reg_addr=0x00(VERSION)）读取版本寄存器；
+2.观察csr_rd_en_o脉冲时序：单周期脉冲，下一周期采样csr_rdata_i；
+3.发送RD_CSR命令（opcode=0x11，reg_addr=0x08(STATUS)）读取状态寄存器；
+4.检查响应帧格式：status(8bit)+rdata(32bit)=40bit；
 期望结果：
-1. test_mode_i=0时：返回STS_NOT_IN_TEST(0x04)，不发起CSR/AHB访问
-2. test_mode_i=1时：返回STS_OK(0x00)，正常执行
+1.RD_CSR(VERSION)：csr_rd_en_o脉冲后下一周期采样csr_rdata_i，响应status_code=STS_OK(0x00)+rdata；
+2.RD_CSR(STATUS)：读取STATUS寄存器，BUSY=0（空闲态），IN_TEST_MODE=1；
+3.读延迟固定1周期，无额外等待；
+coverage check点：
+对CSR读时序csr_rd_en_o→csr_rdata_i延迟采集功能覆盖率</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>TC_008</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>test_csr_address_error</t>
+        </is>
+      </c>
+      <c r="C10" s="11" t="inlineStr">
+        <is>
+          <t>配置条件：
+1.模块复位完成，test_mode_i=1，en_i=1；
+2.lane_mode_i=2'b01（4-bit模式）；
+输入激励：
+1.发送RD_CSR命令（opcode=0x11，reg_addr=0x40）验证地址越界；
+2.发送RD_CSR命令（opcode=0x11，reg_addr=0x3F）验证边界地址（有效）；
+3.发送RD_CSR命令（opcode=0x11，reg_addr=0x00）验证最小地址（有效）；
+4.发送WR_CSR命令（opcode=0x10，reg_addr=0x50，wdata=0x12345678）验证越界写；
+期望结果：
+1.reg_addr=0x40（越界）：返回STS_BAD_REG(0x10)，不发起csr_rd_en_o脉冲；
+2.reg_addr=0x3F（边界）：正常响应（若该地址预留可能返回其他状态）；
+3.reg_addr=0x00（最小）：正常响应status_code=STS_OK(0x00)；
+4.reg_addr=0x50（越界写）：返回STS_BAD_REG(0x10)，不发起csr_wr_en_o脉冲；
+coverage check点：
+对CSR地址范围边界采集功能覆盖率</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>TC_009</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>test_csr_all_registers</t>
+        </is>
+      </c>
+      <c r="C11" s="11" t="inlineStr">
+        <is>
+          <t>配置条件：
+1.模块复位完成，test_mode_i=1，en_i=1；
+2.lane_mode_i随机选择（1-bit或4-bit）；
+输入激励：
+1.遍历所有CSR寄存器地址：VERSION(0x00)、CTRL(0x04)、STATUS(0x08)、LAST_ERR(0x0C)；
+2.对每个寄存器执行RD_CSR读取；
+3.对每个寄存器尝试WR_CSR写入，验证RO/RW属性；
+4.检查写入是否生效或被忽略（RO寄存器）；
+5.重复执行N次（N≥10），每次随机lane_mode；
+期望结果：
+1.VERSION(0x00) RO：读返回版本值，写被忽略；
+2.CTRL(0x04) RW：读写均生效，写入值可读回；
+3.STATUS(0x08) RO：读返回状态，写被忽略；
+4.LAST_ERR(0x0C) RO：读返回最近错误码；
+5.所有读写命令status_code=STS_OK(0x00)；
+coverage check点：
+随机测试，覆盖lane_mode×CSR寄存器的功能覆盖率</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>TC_010</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>test_test_mode_rejection</t>
+        </is>
+      </c>
+      <c r="C12" s="11" t="inlineStr">
+        <is>
+          <t>配置条件：
+1.模块复位完成，en_i=1；
+2.lane_mode_i=2'b01（4-bit模式）；
+输入激励：
+1.设置test_mode_i=0；
+2.发送RD_CSR命令（opcode=0x11，reg_addr=0x00）；
+3.检查响应帧status_code；
+4.检查是否产生csr_rd_en_o脉冲；
+5.发送AHB_WR32命令验证同样被拒绝；
+6.恢复test_mode_i=1，验证命令正常执行；
+期望结果：
+1.test_mode_i=0时：返回STS_NOT_IN_TEST(0x04)；
+2.不发起CSR访问：csr_rd_en_o=0；
+3.不发起AHB访问：htrans_o=IDLE；
+4.test_mode_i=1恢复后命令正常响应STS_OK(0x00)；
+coverage check点：
+对test_mode_i状态采集功能覆盖率</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>TC_011</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>test_en_rejection</t>
+        </is>
+      </c>
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t>配置条件：
+1.模块复位完成，test_mode_i=1；
+2.lane_mode_i=2'b01（4-bit模式）；
+输入激励：
+1.设置en_i=0；
+2.发送RD_CSR命令（opcode=0x11，reg_addr=0x00）；
+3.检查响应帧status_code；
+4.检查是否产生csr_rd_en_o脉冲；
+5.发送AHB_RD32命令验证同样被拒绝；
+6.恢复en_i=1，验证命令正常执行；
+期望结果：
+1.en_i=0时：返回STS_DISABLED(0x08)；
+2.不发起CSR访问：csr_rd_en_o=0，csr_wr_en_o=0；
+3.不发起AHB访问：htrans_o=2'b00(IDLE)；
+4.en_i=1恢复后命令正常响应STS_OK(0x00)；
+coverage check点：
+对en_i状态采集功能覆盖率</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>TC_012</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>test_mode_priority</t>
+        </is>
+      </c>
+      <c r="C14" s="11" t="inlineStr">
+        <is>
+          <t>配置条件：
+1.模块复位完成；
+2.lane_mode_i=2'b01（4-bit模式）；
+输入激励：
+1.设置test_mode_i=0，en_i=0（两个条件同时不满足）；
+2.发送RD_CSR命令（opcode=0x11，reg_addr=0x00）；
+3.检查返回的status_code优先级；
+4.设置test_mode_i=0，en_i=1；
+5.发送命令检查返回STS_NOT_IN_TEST；
+6.设置test_mode_i=1，en_i=0；
+7.发送命令检查返回STS_DISABLED；
+期望结果：
+1.test_mode_i=0且en_i=0时：返回STS_NOT_IN_TEST(0x04)，优先级高于STS_DISABLED(0x08)；
+2.test_mode_i=0，en_i=1时：返回STS_NOT_IN_TEST(0x04)；
+3.test_mode_i=1，en_i=0时：返回STS_DISABLED(0x08)；
+4.所有拒绝场景下无CSR/AHB访问；
+coverage check点：
+验证错误优先级链：STS_NOT_IN_TEST(0x04) &gt; STS_DISABLED(0x08)</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>TC_013</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>test_1bit_lane_mode</t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="inlineStr">
+        <is>
+          <t>配置条件：
+1.模块复位完成，test_mode_i=1，en_i=1；
+2.lane_mode_i=2'b00（1-bit模式）；
+输入激励：
+1.发送RD_CSR命令（opcode=0x11，reg_addr=0x00）；
+2.通过pdi_i[0]按MSB-first方式逐bit发送帧数据，记录接收周期数；
+3.验证仅pdi_i[0]有效，pdi_i[15:1]被忽略；
+4.响应阶段检查pdo_o[0]输出，pdo_o[15:1]=0；
+5.发送WR_CSR命令验证48-bit帧需48周期接收；
+期望结果：
+1.RD_CSR帧(16bit)：需16个周期接收（每周期1bit）；
+2.WR_CSR帧(48bit)：需48个周期接收；
+3.pdi_i[15:1]值不影响接收结果；
+4.pdo_o[15:1]保持为0；
+5.status_code=STS_OK(0x00)；
+coverage check点：
+对1-bit lane模式采集功能覆盖率</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>TC_014</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>test_4bit_lane_mode</t>
+        </is>
+      </c>
+      <c r="C16" s="11" t="inlineStr">
+        <is>
+          <t>配置条件：
+1.模块复位完成，test_mode_i=1，en_i=1；
+2.lane_mode_i=2'b01（4-bit模式）；
+输入激励：
+1.发送RD_CSR命令（opcode=0x11，reg_addr=0x00）；
+2.通过pdi_i[3:0]按MSB-first方式发送帧数据，每周期4bit，记录接收周期数；
+3.验证使用pdi_i[3:0]，按高nibble优先发送；
+4.响应阶段检查pdo_o[3:0]输出；
+5.发送WR_CSR命令验证12周期接收；
+期望结果：
+1.RD_CSR帧(16bit)：需4个周期接收（每周期4bit）；
+2.WR_CSR帧(48bit)：需12个周期接收；
+3.按高nibble优先顺序接收；
+4.pdo_o[15:4]保持为0；
+5.status_code=STS_OK(0x00)；
+coverage check点：
+对4-bit lane模式采集功能覆盖率</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>TC_015</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>test_lane_mode_switching</t>
+        </is>
+      </c>
+      <c r="C17" s="11" t="inlineStr">
+        <is>
+          <t>配置条件：
+1.模块复位完成，test_mode_i=1，en_i=1；
+输入激励：
+1.在pcs_n_i=1空闲期间切换lane_mode_i从2'b00到2'b01；
+2.等待≥2周期同步后拉低pcs_n_i开始新帧；
+3.验证帧接收使用新lane_mode（4周期@4-bit）；
+4.违规测试：在pcs_n_i=0事务期间中途切换lane_mode_i；
+5.继续发送命令，检查帧数据错位或错误状态；
+期望结果：
+1.pcs_n_i=1期间切换：下次事务正常，使用新lane_mode；
+2.pcs_n_i=0期间切换：帧数据损坏，可能导致opcode错误（STS_BAD_OPCODE）或帧中止（STS_FRAME_ERR）；
+3.模块不检测此违规，由集成方保证；
+coverage check点：
+随机测试，覆盖lane_mode切换场景的功能覆盖率</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>TC_016</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>test_frame_transmission</t>
+        </is>
+      </c>
+      <c r="C18" s="11" t="inlineStr">
+        <is>
+          <t>配置条件：
+1.模块复位完成，test_mode_i=1，en_i=1；
+2.lane_mode_i=2'b01（4-bit模式），pcs_n_i初始为高电平；
+输入激励：
+1.ATE拉低pcs_n_i开始帧传输；
+2.按MSB-first顺序通过pdi_i[3:0]发送RD_CSR帧：opcode=0x11 + reg_addr=0x00；
+3.帧接收完成后等待1个turnaround周期；
+4.检查pdo_oe_o拉高，模块驱动pdo_o[3:0]输出响应；
+5.响应帧发送完成后pdo_oe_o拉低，pcs_n_i拉高结束事务；
+期望结果：
+1.请求阶段：pcs_n_i=0期间接收数据，pdo_oe_o=0；
+2.turnaround：固定1周期，pdo_oe_o保持0；
+3.响应阶段：pdo_oe_o=1，模块驱动pdo_o；
+4.status_code=STS_OK(0x00)；
+5.帧边界正确，无总线冲突；
+coverage check点：
+对帧边界和turnaround采集功能覆盖率</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>TC_017</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>test_frame_abort</t>
+        </is>
+      </c>
+      <c r="C19" s="11" t="inlineStr">
+        <is>
+          <t>配置条件：
+1.模块复位完成，test_mode_i=1，en_i=1；
+2.lane_mode_i=2'b01（4-bit模式）；
+输入激励：
+场景1：opcode已锁存后中止
+1.发送WR_CSR命令（opcode=0x10 + reg_addr + wdata）；
+2.在接收第5周期（收到20bit，opcode已锁存8bit）后提前拉高pcs_n_i；
+3.检查返回STS_FRAME_ERR(0x01)；
+场景2：opcode未锁存时中止
+4.发送命令但在接收第1周期（收到4bit，opcode未锁存）后拉高pcs_n_i；
+5.检查不产生frame_abort，静默复位；
+期望结果：
+1.场景1：返回STS_FRAME_ERR(0x01)，pdo_oe_o拉高后输出状态码；
+2.场景2：接收状态静默复位，不产生响应输出；
+3.两种场景均不发起CSR/AHB访问；
+coverage check点：
+对帧中止时机（opcode已锁存/未锁存）采集功能覆盖率</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>TC_018</t>
+        </is>
+      </c>
+      <c r="B20" s="10" t="inlineStr">
+        <is>
+          <t>test_turnaround</t>
+        </is>
+      </c>
+      <c r="C20" s="11" t="inlineStr">
+        <is>
+          <t>配置条件：
+1.模块复位完成，test_mode_i=1，en_i=1；
+2.lane_mode_i=2'b01（4-bit模式）；
+输入激励：
+1.发送RD_CSR命令（opcode=0x11，reg_addr=0x00）；
+2.帧接收完成后观察FSM状态：WAIT_RESP→TA→TX；
+3.在TA态检查pdo_oe_o=0（高阻态）；
+4.进入TX态后检查pdo_oe_o=1（驱动态）；
+5.测量TA持续时间是否为1周期；
+期望结果：
+1.帧接收完成→进入WAIT_RESP等待后端响应；
+2.WAIT_RESP→TA：pdo_oe_o=0保持，总线高阻态；
+3.TA→TX：pdo_oe_o由0变1，开始输出响应；
+4.TA持续时间固定1周期；
+5.无总线冲突；
+coverage check点：
+对turnaround时长采集功能覆盖率</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="10" t="inlineStr">
+        <is>
+          <t>TC_019</t>
+        </is>
+      </c>
+      <c r="B21" s="10" t="inlineStr">
+        <is>
+          <t>test_all_command_frames</t>
+        </is>
+      </c>
+      <c r="C21" s="11" t="inlineStr">
+        <is>
+          <t>配置条件：
+1.模块复位完成，test_mode_i=1，en_i=1；
+2.lane_mode_i=2'b01（4-bit模式）；
+输入激励：
+1.发送WR_CSR命令：opcode=0x10 + reg_addr=0x04 + wdata=0x12345678（48-bit帧，12周期@4-bit）；
+2.发送RD_CSR命令：opcode=0x11 + reg_addr=0x00（16-bit帧，4周期@4-bit）；
+3.发送AHB_WR32命令：opcode=0x20 + addr=0x10000000 + wdata=0xDEADBEEF（72-bit帧，18周期@4-bit）；
+4.发送AHB_RD32命令：opcode=0x21 + addr=0x20000000（40-bit帧，10周期@4-bit）；
+5.验证每种命令的接收周期数；
+期望结果：
+1.WR_CSR帧：接收48-bit需12周期（4-bit模式）；
+2.RD_CSR帧：接收16-bit需4周期；
+3.AHB_WR32帧：接收72-bit需18周期；
+4.AHB_RD32帧：接收40-bit需10周期；
+5.所有命令status_code=STS_OK(0x00)；
+coverage check点：
+对所有opcode帧格式采集功能覆盖率</t>
+        </is>
+      </c>
+      <c r="D21" s="9" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t>TC_020</t>
+        </is>
+      </c>
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>test_response_frames</t>
+        </is>
+      </c>
+      <c r="C22" s="11" t="inlineStr">
+        <is>
+          <t>配置条件：
+1.模块复位完成，test_mode_i=1，en_i=1；
+2.lane_mode_i=2'b01（4-bit模式）；
+输入激励：
+1.发送WR_CSR命令（写命令），验证响应帧仅8-bit status_code；
+2.发送RD_CSR命令（读命令），验证响应帧40-bit：status(8)+rdata(32)；
+3.发送AHB_WR32命令（写命令），验证响应帧8-bit；
+4.发送AHB_RD32命令（读命令），验证响应帧40-bit；
+5.检查响应格式的MSB-first顺序；
+期望结果：
+1.写命令响应：pdo_o输出status(8bit)，4-bit模式下需2周期；
+2.读命令响应：pdo_o输出status(8bit)+rdata(32bit)=40bit，4-bit模式下需10周期；
+3.响应按MSB-first顺序；
+4.所有status_code=STS_OK(0x00)；
+coverage check点：
+对响应帧格式采集功能覆盖率</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="inlineStr">
+        <is>
+          <t>TC_021</t>
+        </is>
+      </c>
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>test_frame_length_boundary</t>
+        </is>
+      </c>
+      <c r="C23" s="11" t="inlineStr">
+        <is>
+          <t>配置条件：
+1.模块复位完成，test_mode_i=1，en_i=1；
+2.随机选择lane_mode（1-bit或4-bit）；
+输入激励：
+1.随机选择命令类型（WR_CSR/RD_CSR/AHB_WR32/AHB_RD32）；
+2.在选定的lane_mode下发送命令，记录接收周期数；
+3.验证接收周期数=帧长度(bit)/lane_width(bit)；
+4.重复执行N次（N≥20），覆盖所有命令×lane_mode组合；
+5.检查响应帧周期数同样符合预期；
+期望结果：
+1.各lane_mode下帧接收周期数正确：
+   - 1-bit：WR_CSR需48周期，RD_CSR需16周期，AHB_WR32需72周期，AHB_RD32需40周期
+   - 4-bit：WR_CSR需12周期，RD_CSR需4周期，AHB_WR32需18周期，AHB_RD32需10周期
+2.响应周期数同样正确；
+3.所有命令正常响应；
+coverage check点：
+随机测试，覆盖lane_mode×opcode组合的功能覆盖率</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="inlineStr">
+        <is>
+          <t>TC_022</t>
+        </is>
+      </c>
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>test_valid_opcodes</t>
+        </is>
+      </c>
+      <c r="C24" s="11" t="inlineStr">
+        <is>
+          <t>配置条件：
+1.模块复位完成，test_mode_i=1，en_i=1；
+2.lane_mode_i=2'b01（4-bit模式）；
+输入激励：
+1.发送opcode=0x10命令，验证WR_CSR路径：产生csr_wr_en_o脉冲；
+2.发送opcode=0x11命令，验证RD_CSR路径：产生csr_rd_en_o脉冲；
+3.发送opcode=0x20命令，验证AHB_WR32路径：产生htrans=NONSEQ+hwrite=1；
+4.发送opcode=0x21命令，验证AHB_RD32路径：产生htrans=NONSEQ+hwrite=0；
+5.检查每种opcode的内部译码结果正确；
+期望结果：
+1.0x10→WR_CSR：cmd_type指示CSR写，csr_wr_en_o脉冲；
+2.0x11→RD_CSR：cmd_type指示CSR读，csr_rd_en_o脉冲；
+3.0x20→AHB_WR32：cmd_type指示AHB写，htrans_o=2'b10(NONSEQ)，hwrite_o=1；
+4.0x21→AHB_RD32：cmd_type指示AHB读，htrans_o=2'b10，hwrite_o=0；
+5.所有命令status_code=STS_OK(0x00)；
+coverage check点：
+对所有有效opcode采集功能覆盖率</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="inlineStr">
+        <is>
+          <t>TC_023</t>
+        </is>
+      </c>
+      <c r="B25" s="10" t="inlineStr">
+        <is>
+          <t>test_illegal_opcode</t>
+        </is>
+      </c>
+      <c r="C25" s="11" t="inlineStr">
+        <is>
+          <t>配置条件：
+1.模块复位完成，test_mode_i=1，en_i=1；
+2.lane_mode_i=2'b01（4-bit模式）；
+输入激励：
+1.发送opcode=0x00（非法），验证返回STS_BAD_OPCODE(0x02)；
+2.发送opcode=0x0F（非法边界），验证返回STS_BAD_OPCODE；
+3.发送opcode=0x12（非法，在0x11和0x20之间），验证返回STS_BAD_OPCODE；
+4.发送opcode=0xFF（非法边界），验证返回STS_BAD_OPCODE；
+5.随机选择N个（N≥10）非法opcode（0x00~0x0F，0x12~0x1F，0x22~0xFF）验证；
+6.检查不发起CSR/AHB访问；
+期望结果：
+1.所有非法opcode返回STS_BAD_OPCODE(0x02)；
+2.opcode检查在前置检查阶段，不发起任何CSR/AHB访问；
+3.csr_wr_en_o=0，csr_rd_en_o=0，htrans_o=IDLE；
+4.错误优先级正确；
+coverage check点：
+随机测试，覆盖非法opcode范围的功能覆盖率</t>
+        </is>
+      </c>
+      <c r="D25" s="9" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="10" t="inlineStr">
+        <is>
+          <t>TC_024</t>
+        </is>
+      </c>
+      <c r="B26" s="10" t="inlineStr">
+        <is>
+          <t>test_opcode_boundary</t>
+        </is>
+      </c>
+      <c r="C26" s="11" t="inlineStr">
+        <is>
+          <t>配置条件：
+1.模块复位完成，test_mode_i=1，en_i=1；
+2.lane_mode_i=2'b01（4-bit模式）；
+输入激励：
+1.发送opcode=0x0F（非法，与有效0x10相邻）验证返回STS_BAD_OPCODE；
+2.发送opcode=0x10（有效边界）验证正常译码为WR_CSR；
+3.发送opcode=0x11（有效）验证正常译码为RD_CSR；
+4.发送opcode=0x12（非法，与有效0x11相邻）验证返回STS_BAD_OPCODE；
+5.发送opcode=0x1F（非法）验证返回STS_BAD_OPCODE；
+6.发送opcode=0x20（有效边界）验证正常译码为AHB_WR32；
+期望结果：
+1.opcode边界值正确区分有效/非法：
+   - 有效：0x10(WR_CSR)、0x11(RD_CSR)、0x20(AHB_WR32)、0x21(AHB_RD32)
+   - 非法：其他所有值
+2.有效opcode正常执行，非法返回STS_BAD_OPCODE(0x02)；
+coverage check点：
+对opcode边界值采集功能覆盖率</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="10" t="inlineStr">
+        <is>
+          <t>TC_025</t>
+        </is>
+      </c>
+      <c r="B27" s="10" t="inlineStr">
+        <is>
+          <t>test_lane_mode_config</t>
+        </is>
+      </c>
+      <c r="C27" s="11" t="inlineStr">
+        <is>
+          <t>配置条件：
+1.模块复位完成，test_mode_i=1，en_i=1；
+2.lane_mode_i初始为2'b00（1-bit）；
+输入激励：
+1.通过WR_CSR命令配置CTRL.LANE_MODE=2'b01（4-bit模式）；
+2.发送RD_CSR命令读取CTRL验证配置；
+3.发送RD_CSR命令测试帧接收，验证使用4-bit模式（4周期接收16bit）；
+4.通过WR_CSR命令配置CTRL.LANE_MODE=2'b00（1-bit）；
+5.再次发送命令验证使用1-bit模式（16周期接收16bit）；
+期望结果：
+1.CTRL.LANE_MODE写入成功，可读回；
+2.配置后帧收发使用新lane模式；
+3.LANE_MODE仅支持00(1-bit)和01(4-bit)，MVP不支持10/11；
+4.帧接收周期数符合lane模式；
+coverage check点：
+对LANE_MODE配置切换采集功能覆盖率</t>
+        </is>
+      </c>
+      <c r="D27" s="9" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="10" t="inlineStr">
+        <is>
+          <t>TC_026</t>
+        </is>
+      </c>
+      <c r="B28" s="10" t="inlineStr">
+        <is>
+          <t>test_soft_reset</t>
+        </is>
+      </c>
+      <c r="C28" s="11" t="inlineStr">
+        <is>
+          <t>配置条件：
+1.模块复位完成，test_mode_i=1，en_i=1；
+2.lane_mode_i=2'b01（4-bit模式）；
+输入激励：
+1.发送WR_CSR命令配置CTRL.EN=1，LANE_MODE=01；
+2.发送RD_CSR命令验证配置；
+3.发送WR_CSR命令写入CTRL.SOFT_RST=1触发软复位；
+4.检查协议上下文是否清零；
+5.读取CTRL验证LANE_MODE恢复默认值2'b00；
+6.发送RD_CSR命令验证模块正常工作；
+期望结果：
+1.SOFT_RST=1后：协议上下文清空，LANE_MODE恢复2'b00（1-bit默认）；
+2.FSM状态回到IDLE；
+3.软复位不影响CTRL.EN（由硬件端口en_i控制）；
+4.复位后模块正常接受新命令；
+coverage check点：
+对SOFT_RST触发采集功能覆盖率</t>
+        </is>
+      </c>
+      <c r="D28" s="9" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="10" t="inlineStr">
+        <is>
+          <t>TC_027</t>
+        </is>
+      </c>
+      <c r="B29" s="10" t="inlineStr">
+        <is>
+          <t>test_config_timing</t>
+        </is>
+      </c>
+      <c r="C29" s="11" t="inlineStr">
+        <is>
+          <t>配置条件：
+1.模块复位完成，test_mode_i=1，en_i=1；
+2.pcs_n_i=1（空闲态）；
+输入激励：
+1.在pcs_n_i=1期间切换lane_mode_i从2'b00到2'b01；
+2.等待≥2个clk_i周期做同步；
+3.拉低pcs_n_i开始新帧，验证使用新lane_mode；
+4.测试不等足够周期（如只等1周期）就开始新帧，检查行为；
+5.测试在pcs_n_i=0期间切换lane_mode（违规）；
+期望结果：
+1.pcs_n_i=1期间切换并等待≥2周期后新帧正常；
+2.不等足够周期可能导致lane_mode未同步，帧数据错位；
+3.pcs_n_i=0期间切换导致帧损坏（模块不检测）；
+4.lane_mode需在事务边界切换；
+coverage check点：
+对lane_mode切换时序采集功能覆盖率</t>
+        </is>
+      </c>
+      <c r="D29" s="9" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="10" t="inlineStr">
+        <is>
+          <t>TC_028</t>
+        </is>
+      </c>
+      <c r="B30" s="10" t="inlineStr">
+        <is>
+          <t>test_status_polling</t>
+        </is>
+      </c>
+      <c r="C30" s="11" t="inlineStr">
+        <is>
+          <t>配置条件：
+1.模块复位完成，test_mode_i=1，en_i=1；
+2.lane_mode_i=2'b01（4-bit模式）；
+输入激励：
+1.检查模块无独立中断输出端口（IRQ）；
+2.发送命令（成功/失败）；
+3.通过RD_CSR读取STATUS寄存器获取状态；
+4.通过RD_CSR读取LAST_ERR寄存器获取最近错误码；
+5.测试sticky位的清除（写1清零，WC属性）；
+期望结果：
+1.MVP版本无独立中断输出；
+2.STATUS寄存器反映当前状态：BUSY、RESP_VALID、CMD_ERR等位；
+3.LAST_ERR存储最近错误码，新命令开始后覆盖；
+4.所有状态通过寄存器轮询获取；
 coverage check点：
 直接用例覆盖，不收功能覆盖率</t>
         </is>
       </c>
-      <c r="D9" s="9" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="10" t="inlineStr">
-        <is>
-          <t>DV_TC_008</t>
-        </is>
-      </c>
-      <c r="B10" s="10" t="inlineStr">
-        <is>
-          <t>en_reject_test</t>
-        </is>
-      </c>
-      <c r="C10" s="24" t="inlineStr">
+      <c r="D30" s="9" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="10" t="inlineStr">
+        <is>
+          <t>TC_029</t>
+        </is>
+      </c>
+      <c r="B31" s="10" t="inlineStr">
+        <is>
+          <t>test_error_priority_chain</t>
+        </is>
+      </c>
+      <c r="C31" s="11" t="inlineStr">
         <is>
           <t>配置条件：
-1. 模块复位完成，lane_mode_i=2'b01（4-bit）
+1.模块复位完成；
+2.lane_mode_i=2'b01；
 输入激励：
-1. 设置test_mode_i=1，en_i=0
-2. 发送WR_CSR命令：opcode=0x10，reg_addr=0x04，wdata=0x00000001
-3. 检查响应帧status_code
-4. 再设置en_i=1，发送同一命令验证恢复正常
+1.构造多错误并发场景：发送非法opcode(0xFF)且test_mode_i=0且en_i=0；
+   → 验证返回STS_FRAME_ERR(0x01)（最高优先级，因帧结构损坏优先判断）；
+   注：实际上frame_abort来自pcs_n_i提前释放，此处改为：
+   设置pcs_n_i提前拉高触发frame_abort + 其他错误条件；
+2.发送非法opcode(0xFF)且test_mode_i=1且en_i=1；
+   → 返回STS_BAD_OPCODE(0x02)；
+3.test_mode_i=0且en_i=0；
+   → 返回STS_NOT_IN_TEST(0x04)（优先于STS_DISABLED）；
+4.test_mode_i=1且en_i=0；
+   → 返回STS_DISABLED(0x08)；
+5.发送CSR命令reg_addr=0x40；
+   → 返回STS_BAD_REG(0x10)；
+6.发送AHB命令addr=0x00000001（非对齐）；
+   → 返回STS_ALIGN_ERR(0x20)；
 期望结果：
-1. en_i=0时：返回STS_DISABLED(0x08)，不发起CSR/AHB访问
-2. en_i=1时：返回STS_OK(0x00)，正常执行
+1.错误优先级链：0x01&gt;0x02&gt;0x04&gt;0x08&gt;0x10&gt;0x20；
+2.仅返回最高优先级错误，不累积；
+3.前置错误均不发起CSR/AHB访问；
+coverage check点：
+对错误优先级链采集功能覆盖率</t>
+        </is>
+      </c>
+      <c r="D31" s="9" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="10" t="inlineStr">
+        <is>
+          <t>TC_030</t>
+        </is>
+      </c>
+      <c r="B32" s="10" t="inlineStr">
+        <is>
+          <t>test_ahb_error_response</t>
+        </is>
+      </c>
+      <c r="C32" s="11" t="inlineStr">
+        <is>
+          <t>配置条件：
+1.模块复位完成，test_mode_i=1，en_i=1；
+2.lane_mode_i=2'b01（4-bit模式）；
+3.AHB Slave配置为返回错误响应；
+输入激励：
+1.发送AHB_RD32命令（opcode=0x21，addr=0x10000000）；
+2.配置AHB Slave在数据相返回hresp_i=1；
+3.检查模块返回STS_AHB_ERR(0x40)；
+4.检查AXI FSM进入AXI_ERR状态；
+5.检查AHB输出恢复空闲（htrans_o=IDLE）；
+6.恢复Slave正常响应，发送新命令验证恢复；
+期望结果：
+1.hresp_i=1时返回STS_AHB_ERR(0x40)；
+2.AXI FSM：AXI_WAIT→AXI_ERR→AXI_IDLE；
+3.错误响应后AHB输出空闲，可接受新请求；
+4.新命令正常响应；
+coverage check点：
+对hresp_i错误响应采集功能覆盖率</t>
+        </is>
+      </c>
+      <c r="D32" s="9" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="10" t="inlineStr">
+        <is>
+          <t>TC_031</t>
+        </is>
+      </c>
+      <c r="B33" s="10" t="inlineStr">
+        <is>
+          <t>test_ahb_timeout</t>
+        </is>
+      </c>
+      <c r="C33" s="11" t="inlineStr">
+        <is>
+          <t>配置条件：
+1.模块复位完成，test_mode_i=1，en_i=1；
+2.lane_mode_i=2'b01；
+3.AHB Slave配置为持续不响应；
+输入激励：
+1.发送AHB_WR32命令（opcode=0x20，addr=0x10000000，wdata=0x12345678）；
+2.配置AHB Slave保持hready_i=0，不返回响应；
+3.等待超过BUS_TIMEOUT_CYCLES(256)周期；
+4.检查模块返回STS_AHB_ERR(0x40)；
+5.检查超时计数器达到阈值后触发AXI_ERR；
+6.恢复Slave响应，发送新命令验证；
+期望结果：
+1.hready_i=0持续256周期后触发超时；
+2.返回STS_AHB_ERR(0x40)，与hresp_i错误使用相同状态码；
+3.timeout_cnt从0计数到255后触发AXI_ERR；
+4.AHB输出恢复空闲；
+coverage check点：
+对AHB超时采集功能覆盖率</t>
+        </is>
+      </c>
+      <c r="D33" s="9" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="10" t="inlineStr">
+        <is>
+          <t>TC_032</t>
+        </is>
+      </c>
+      <c r="B34" s="10" t="inlineStr">
+        <is>
+          <t>test_frame_error</t>
+        </is>
+      </c>
+      <c r="C34" s="11" t="inlineStr">
+        <is>
+          <t>配置条件：
+1.模块复位完成，test_mode_i=1，en_i=1；
+2.lane_mode_i=2'b01；
+输入激励：
+帧中止(FRAME_ERR)场景：
+1.发送WR_CSR命令，在接收中途（如收到24bit）提前拉高pcs_n_i；
+2.检查返回STS_FRAME_ERR(0x01)；
+3.检查不发起CSR访问；
+非对齐地址(ALIGN_ERR)场景：
+4.发送AHB_WR32命令addr=0x10000001（addr[1:0]!=0）；
+5.检查返回STS_ALIGN_ERR(0x20)；
+6.检查不发起AHB访问；
+期望结果：
+1.帧中止：返回STS_FRAME_ERR(0x01)，pdo_oe_o拉高后输出状态码；
+2.非对齐地址：返回STS_ALIGN_ERR(0x20)，不发起AHB事务；
+3.两种错误均为前置检查，不产生总线访问；
+coverage check点：
+对FRAME_ERR和ALIGN_ERR采集功能覆盖率</t>
+        </is>
+      </c>
+      <c r="D34" s="9" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="10" t="inlineStr">
+        <is>
+          <t>TC_033</t>
+        </is>
+      </c>
+      <c r="B35" s="10" t="inlineStr">
+        <is>
+          <t>test_random_error_injection</t>
+        </is>
+      </c>
+      <c r="C35" s="11" t="inlineStr">
+        <is>
+          <t>配置条件：
+1.模块复位完成，test_mode_i=1，en_i=1；
+2.随机选择lane_mode；
+输入激励：
+随机注入以下错误类型之一：
+1.非法opcode：随机选择0x00~0x0F或0x12~0x1F或0x22~0xFF；
+   → 期望返回STS_BAD_OPCODE(0x02)
+2.非对齐地址：随机设置addr[1:0]!=0；
+   → 期望返回STS_ALIGN_ERR(0x20)
+3.CSR地址越界：随机reg_addr&gt;=0x40；
+   → 期望返回STS_BAD_REG(0x10)
+4.AHB错误响应：配置hresp_i=1；
+   → 期望返回STS_AHB_ERR(0x40)
+5.AHB超时：配置hready_i=0持续&gt;256周期；
+   → 期望返回STS_AHB_ERR(0x40)
+每种错误类型重复执行N次（N≥10）；
+期望结果：
+1.每种错误返回对应的状态码；
+2.前置错误不发起总线访问；
+3.执行期错误正确处理并恢复；
+coverage check点：
+随机测试，覆盖所有错误类型的场景功能覆盖率</t>
+        </is>
+      </c>
+      <c r="D35" s="9" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="10" t="inlineStr">
+        <is>
+          <t>TC_034</t>
+        </is>
+      </c>
+      <c r="B36" s="10" t="inlineStr">
+        <is>
+          <t>test_idle_power</t>
+        </is>
+      </c>
+      <c r="C36" s="11" t="inlineStr">
+        <is>
+          <t>配置条件：
+1.模块复位完成；
+2.pcs_n_i=1保持空闲态；
+输入激励：
+1.保持pcs_n_i=1超过100个时钟周期；
+2.检查RX移位寄存器rx_shift_q不更新；
+3.检查TX移位寄存器tx_shift_q不翻转；
+4.检查超时计数器timeout_cnt不工作（非AXI_WAIT状态）；
+5.检查关键寄存器无多余翻转；
+6.发送一条命令唤醒，验证正常工作；
+期望结果：
+1.空闲态：rx_shift_q、tx_shift_q保持，不翻转；
+2.超时计数器仅在AXI_WAIT计数；
+3.test_mode_i=0时AHB输出保持IDLE；
+4.唤醒后模块正常响应命令；
 coverage check点：
 直接用例覆盖，不收功能覆盖率</t>
         </is>
       </c>
-      <c r="D10" s="9" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="10" t="inlineStr">
-        <is>
-          <t>DV_TC_009</t>
-        </is>
-      </c>
-      <c r="B11" s="10" t="inlineStr">
-        <is>
-          <t>mode_priority_test</t>
-        </is>
-      </c>
-      <c r="C11" s="24" t="inlineStr">
+      <c r="D36" s="9" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="10" t="inlineStr">
+        <is>
+          <t>TC_035</t>
+        </is>
+      </c>
+      <c r="B37" s="10" t="inlineStr">
+        <is>
+          <t>test_clock_gating</t>
+        </is>
+      </c>
+      <c r="C37" s="11" t="inlineStr">
         <is>
           <t>配置条件：
-1. 模块复位完成
+1.模块复位完成；
+2.lane_mode_i=2'b01；
 输入激励：
-1. 设置test_mode_i=0且en_i=0，发送RD_CSR命令（opcode=0x11, reg_addr=0x00），检查status_code
-2. 设置test_mode_i=0且en_i=1，发送同一命令，检查status_code
-3. 设置test_mode_i=1且en_i=0，发送同一命令，检查status_code
+1.设置test_mode_i=0；
+2.检查htrans_o保持2'b00(IDLE)；
+3.检查hburst_o=3'b000(SINGLE)；
+4.检查haddr_o=0或保持上一值；
+5.检查超时计数器仅在AXI_WAIT状态工作；
+6.发送命令验证被拒绝；
 期望结果：
-1. test_mode_i=0且en_i=0：返回STS_NOT_IN_TEST(0x04)（优先级高于STS_DISABLED）
-2. test_mode_i=0且en_i=1：返回STS_NOT_IN_TEST(0x04)
-3. test_mode_i=1且en_i=0：返回STS_DISABLED(0x08)
-4. 错误优先级正确：STS_NOT_IN_TEST(0x04) &gt; STS_DISABLED(0x08)
+1.test_mode_i=0时：AHB输出保持空闲；
+2.超时计数器门控条件：state!=AXI_WAIT；
+3.RX门控条件：pcs_n_i=1；
+4.TX门控条件：非TX态；
+5.低功耗设计正确生效；
 coverage check点：
 直接用例覆盖，不收功能覆盖率</t>
         </is>
       </c>
-      <c r="D11" s="9" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="10" t="inlineStr">
-        <is>
-          <t>DV_TC_010</t>
-        </is>
-      </c>
-      <c r="B12" s="10" t="inlineStr">
-        <is>
-          <t>lane_1bit_mode_test</t>
-        </is>
-      </c>
-      <c r="C12" s="24" t="inlineStr">
+      <c r="D37" s="9" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="10" t="inlineStr">
+        <is>
+          <t>TC_036</t>
+        </is>
+      </c>
+      <c r="B38" s="10" t="inlineStr">
+        <is>
+          <t>test_latency_measurement</t>
+        </is>
+      </c>
+      <c r="C38" s="11" t="inlineStr">
         <is>
           <t>配置条件：
-1. 模块复位完成，test_mode_i=1，en_i=1
-2. 设置lane_mode_i=2'b00（1-bit模式）
+1.模块复位完成，test_mode_i=1，en_i=1；
+2.lane_mode_i=2'b01（4-bit模式）；
+3.clk_i=100MHz；
 输入激励：
-1. 发送RD_CSR命令：opcode=0x11，reg_addr=0x00
-2. 检查接收周期数：16bit帧需16周期接收（仅使用pdi_i[0]）
-3. 检查响应周期数：40bit响应需40周期发送（仅使用pdo_o[0]）
+1.发送AHB_RD32命令，测量从pcs_n_i拉低到响应完成的周期数；
+   计算：RX(10)+译码(2)+AHB(2)+TA(1)+TX(10)≈23~24周期；
+2.发送AHB_WR32命令，测量端到端延时；
+   计算：RX(18)+译码(2)+AHB(2)+TA(1)+TX(2)≈23周期；
+3.发送WR_CSR命令，测量延时；
+   计算：RX(12)+执行(1)+TA(1)+TX(2)≈16周期；
+4.切换到1-bit模式重复测量；
 期望结果：
-1. 仅使用pdi_i[0]/pdo_o[0]，其余位忽略
-2. RD_CSR命令16bit帧需16周期接收
-3. 响应status_code=STS_OK(0x00)
+1.4-bit模式AHB_RD32最小延时约23~24周期；
+2.4-bit模式AHB_WR32最小延时约23周期；
+3.4-bit模式WR_CSR最小延时约16周期；
+4.1-bit模式延时约为4-bit的4倍；
 coverage check点：
-覆盖lane_mode=2'b00</t>
-        </is>
-      </c>
-      <c r="D12" s="9" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="10" t="inlineStr">
-        <is>
-          <t>DV_TC_011</t>
-        </is>
-      </c>
-      <c r="B13" s="10" t="inlineStr">
-        <is>
-          <t>lane_4bit_mode_test</t>
-        </is>
-      </c>
-      <c r="C13" s="24" t="inlineStr">
+对端到端延时采集功能覆盖率</t>
+        </is>
+      </c>
+      <c r="D38" s="9" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="10" t="inlineStr">
+        <is>
+          <t>TC_037</t>
+        </is>
+      </c>
+      <c r="B39" s="10" t="inlineStr">
+        <is>
+          <t>test_address_alignment</t>
+        </is>
+      </c>
+      <c r="C39" s="11" t="inlineStr">
         <is>
           <t>配置条件：
-1. 模块复位完成，test_mode_i=1，en_i=1
-2. 设置lane_mode_i=2'b01（4-bit模式）
+1.模块复位完成，test_mode_i=1，en_i=1；
+2.lane_mode_i=2'b01；
 输入激励：
-1. 发送RD_CSR命令：opcode=0x11，reg_addr=0x00
-2. 检查接收周期数：16bit帧需4周期接收（使用pdi_i[3:0]）
-3. 检查响应周期数：40bit响应需10周期发送（使用pdo_o[3:0]）
+1.发送AHB_WR32命令addr=0x10000000（对齐，addr[1:0]=00）；
+2.验证正常执行，返回STS_OK(0x00)；
+3.发送AHB_WR32命令addr=0x10000001（非对齐，addr[1:0]=01）；
+4.验证返回STS_ALIGN_ERR(0x20)；
+5.发送AHB_RD32命令addr=0x10000002（非对齐）验证；
+6.发送AHB_RD32命令addr=0x10000003（非对齐）验证；
+7.检查非对齐地址不发起AHB事务；
 期望结果：
-1. 使用pdi_i[3:0]/pdo_o[3:0]，按高nibble优先发送
-2. RD_CSR命令16bit帧需4周期接收
-3. 响应status_code=STS_OK(0x00)
+1.对齐地址(addr[1:0]=00)：正常访问，status_code=STS_OK；
+2.非对齐地址(addr[1:0]!=00)：返回STS_ALIGN_ERR(0x20)；
+3.非对齐地址不发起AHB访问：htrans_o保持IDLE；
+4.hsize_o固定为WORD(3'b010)，不支持byte/halfword；
 coverage check点：
-覆盖lane_mode=2'b01</t>
-        </is>
-      </c>
-      <c r="D13" s="9" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="10" t="inlineStr">
-        <is>
-          <t>DV_TC_012</t>
-        </is>
-      </c>
-      <c r="B14" s="10" t="inlineStr">
-        <is>
-          <t>lane_mode_random_test</t>
-        </is>
-      </c>
-      <c r="C14" s="24" t="inlineStr">
+对地址对齐检查采集功能覆盖率</t>
+        </is>
+      </c>
+      <c r="D39" s="9" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="10" t="inlineStr">
+        <is>
+          <t>TC_038</t>
+        </is>
+      </c>
+      <c r="B40" s="10" t="inlineStr">
+        <is>
+          <t>test_random_config_throughput</t>
+        </is>
+      </c>
+      <c r="C40" s="11" t="inlineStr">
         <is>
           <t>配置条件：
-1. 模块复位完成，test_mode_i=1，en_i=1
+1.模块复位完成，test_mode_i=1，en_i=1；
+2.随机lane_mode（1-bit或4-bit）；
 输入激励：
-1. 随机切换lane_mode_i（2'b00/01），每次切换后等待pcs_n_i=1空闲态
-2. 在当前lane_mode下发送RD_CSR命令（opcode=0x11, reg_addr=0x00）
-3. 重复执行N次（N≥20），每次随机配置lane_mode
+1.随机选择lane_mode：2'b00(1-bit)或2'b01(4-bit)；
+2.随机选择opcode：0x10/0x11/0x20/0x21；
+3.发送命令，测量端到端延时；
+4.记录延时值并与理论值对比；
+5.重复执行N次（N≥20），覆盖lane_mode×opcode所有组合；
+6.计算实际吞吐率；
 期望结果：
-1. 帧收发正确，周期数符合预期（1-bit: 16周期，4-bit: 4周期）
-2. 所有命令返回status_code=STS_OK(0x00)
+1.各组合延时符合理论预期；
+2.4-bit模式：RD_CSR≈6周期，WR_CSR≈16周期，AHB_RD32≈24周期，AHB_WR32≈23周期；
+3.1-bit模式：各命令延时约为4-bit的4倍；
+4.吞吐率：4-bit约30MB/s，1-bit约7.5MB/s；
 coverage check点：
-覆盖lane_mode=2'b00和2'b01，覆盖lane_mode × opcode(0x11)组合</t>
-        </is>
-      </c>
-      <c r="D14" s="9" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="10" t="inlineStr">
-        <is>
-          <t>DV_TC_013</t>
-        </is>
-      </c>
-      <c r="B15" s="10" t="inlineStr">
-        <is>
-          <t>frame_transmit_test</t>
-        </is>
-      </c>
-      <c r="C15" s="24" t="inlineStr">
+随机测试，覆盖lane_mode×opcode组合的延时功能覆盖率</t>
+        </is>
+      </c>
+      <c r="D40" s="9" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="10" t="inlineStr">
+        <is>
+          <t>TC_039</t>
+        </is>
+      </c>
+      <c r="B41" s="10" t="inlineStr">
+        <is>
+          <t>test_debug_observability</t>
+        </is>
+      </c>
+      <c r="C41" s="11" t="inlineStr">
         <is>
           <t>配置条件：
-1. 模块复位完成，test_mode_i=1，en_i=1
-2. 配置LANE_MODE=01（4-bit模式），pcs_n_i初始为高电平
+1.模块复位完成，test_mode_i=1，en_i=1；
+2.lane_mode_i=2'b01；
 输入激励：
-1. ATE拉低pcs_n_i开始帧传输
-2. 按MSB-first顺序通过pdi_i[3:0]发送RD_CSR帧：opcode=0x11 + reg_addr=0x00
-3. 等待1个turnaround周期
-4. 检查pdo_oe_o拉高，模块驱动pdo_o[3:0]输出响应
+1.发送WR_CSR命令（opcode=0x10，reg_addr=0x04，wdata=0x01）；
+2.检查内部可观测点：
+   - front_state：观察IDLE→ISSUE→WAIT_RESP→TA→TX状态变化
+   - opcode_latched_q：锁存值=0x10
+   - addr暂存值：N/A（CSR命令）
+   - wdata暂存值：0x00000001
+   - status_code：STS_OK(0x00)
+3.发送AHB_RD32命令；
+4.观察：
+   - axi_state：AXI_IDLE→AXI_REQ→AXI_WAIT→AXI_DONE
+   - haddr_o：验证地址值
+   - hrdata_i：验证读数据
+   - status_code
 期望结果：
-1. pcs_n_i=0期间接收数据，turnaround后pdo_oe_o=1驱动响应
-2. 响应帧格式正确：status_code + rdata
+1.所有状态机状态变化可观测；
+2.opcode、addr、wdata、rdata、status_code正确反映；
+3.错误场景下LAST_ERR可观测到错误码；
+4.DFX可观测点覆盖关键内部状态；
 coverage check点：
 直接用例覆盖，不收功能覆盖率</t>
         </is>
       </c>
-      <c r="D15" s="9" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="10" t="inlineStr">
-        <is>
-          <t>DV_TC_014</t>
-        </is>
-      </c>
-      <c r="B16" s="10" t="inlineStr">
-        <is>
-          <t>frame_abort_test</t>
-        </is>
-      </c>
-      <c r="C16" s="24" t="inlineStr">
+      <c r="D41" s="9" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="10" t="inlineStr">
+        <is>
+          <t>TC_040</t>
+        </is>
+      </c>
+      <c r="B42" s="10" t="inlineStr">
+        <is>
+          <t>test_random_debug_observability</t>
+        </is>
+      </c>
+      <c r="C42" s="11" t="inlineStr">
         <is>
           <t>配置条件：
-1. 模块复位完成，test_mode_i=1，en_i=1
-2. 配置LANE_MODE=01（4-bit模式）
+1.模块复位完成，test_mode_i=1，en_i=1；
+2.随机lane_mode；
 输入激励：
-1. 拉低pcs_n_i开始发送WR_CSR命令（opcode=0x10）
-2. 在接收中途（已发送8bit后，rx_count=8 &lt; expected_rx_bits=48）提前拉高pcs_n_i
-3. 检查frame_abort信号和错误处理
+1.随机选择命令类型（WR_CSR/RD_CSR/AHB_WR32/AHB_RD32）；
+2.随机选择成功或失败场景：
+   - 成功：正常参数
+   - 失败：注入错误（非法opcode、非对齐地址等）
+3.执行命令，记录内部观测点状态；
+4.验证观测点状态与命令执行一致；
+5.重复执行N次（N≥15）；
 期望结果：
-1. 返回STS_FRAME_ERR(0x01)
-2. pdo_oe_o拉高后输出状态码0x01
-3. 不发起CSR/AHB访问
+1.成功场景：观测到正常状态流，status_code=STS_OK；
+2.失败场景：观测到错误状态，status_code=对应错误码；
+3.ERR状态机观测：前置错误不进入AXI FSM；
+4.状态观测与实际执行一致；
+coverage check点：
+随机测试，覆盖各种场景的DFX可观测性功能覆盖率</t>
+        </is>
+      </c>
+      <c r="D42" s="9" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="10" t="inlineStr">
+        <is>
+          <t>TC_041</t>
+        </is>
+      </c>
+      <c r="B43" s="10" t="inlineStr">
+        <is>
+          <t>test_memory_map</t>
+        </is>
+      </c>
+      <c r="C43" s="11" t="inlineStr">
+        <is>
+          <t>配置条件：
+1.模块复位完成，test_mode_i=1，en_i=1；
+2.lane_mode_i=2'b01；
+输入激励：
+1.通过WR_CSR/RD_CSR访问模块CSR（opcode=0x10/0x11）；
+   验证CSR不产生AHB事务，无htrans_o脉冲；
+2.通过AHB_WR32/AHB_RD32访问SoC AHB fabric；
+   验证产生htrans_o=NONSEQ；
+3.检查AHB Master地址空间：
+   - 使用32-bit地址
+   - WORD访问粒度（hsize=3'b010）
+4.验证CSR地址(0x00~0x3F)与AHB地址空间独立；
+期望结果：
+1.CSR通过协议命令访问，不进入AHB memory map；
+2.AHB Master使用32-bit地址访问SoC；
+3.CSR访问不产生htrans_o脉冲；
+4.Memory map分离正确；
 coverage check点：
 直接用例覆盖，不收功能覆盖率</t>
         </is>
       </c>
-      <c r="D16" s="9" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="10" t="inlineStr">
-        <is>
-          <t>DV_TC_015</t>
-        </is>
-      </c>
-      <c r="B17" s="10" t="inlineStr">
-        <is>
-          <t>turnaround_test</t>
-        </is>
-      </c>
-      <c r="C17" s="24" t="inlineStr">
-        <is>
-          <t>配置条件：
-1. 模块复位完成，test_mode_i=1，en_i=1
-2. 配置LANE_MODE=01（4-bit模式）
-输入激励：
-1. 发送完整RD_CSR帧（opcode=0x11 + reg_addr=0x00）
-2. 精确测量从帧接收完成到pdo_oe_o拉高之间的周期数
-期望结果：
-1. turnaround固定1个clk_i周期
-2. pdo_oe_o在turnaround结束后拉高
-coverage check点：
-直接用例覆盖，不收功能覆盖率</t>
-        </is>
-      </c>
-      <c r="D17" s="9" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="10" t="inlineStr">
-        <is>
-          <t>DV_TC_016</t>
-        </is>
-      </c>
-      <c r="B18" s="10" t="inlineStr">
-        <is>
-          <t>command_frame_length_test</t>
-        </is>
-      </c>
-      <c r="C18" s="24" t="inlineStr">
-        <is>
-          <t>配置条件：
-1. 模块复位完成，test_mode_i=1，en_i=1
-2. 配置LANE_MODE=01（4-bit模式）
-输入激励：
-1. 发送WR_CSR帧：48bit（opcode8+reg_addr8+wdata32）=12周期@4-bit
-2. 发送RD_CSR帧：16bit（opcode8+reg_addr8）=4周期@4-bit
-3. 发送AHB_WR32帧：72bit（opcode8+addr32+wdata32）=18周期@4-bit
-4. 发送AHB_RD32帧：40bit（opcode8+addr32）=10周期@4-bit
-期望结果：
-1. 各命令帧接收周期数符合预期
-2. 所有命令返回正确的status_code
-coverage check点：
-直接用例覆盖，不收功能覆盖率</t>
-        </is>
-      </c>
-      <c r="D18" s="9" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="10" t="inlineStr">
-        <is>
-          <t>DV_TC_017</t>
-        </is>
-      </c>
-      <c r="B19" s="10" t="inlineStr">
-        <is>
-          <t>response_frame_length_test</t>
-        </is>
-      </c>
-      <c r="C19" s="24" t="inlineStr">
-        <is>
-          <t>配置条件：
-1. 模块复位完成，test_mode_i=1，en_i=1
-2. 配置LANE_MODE=01（4-bit模式）
-输入激励：
-1. 发送WR_CSR命令，验证写命令响应帧：8bit status_code=2周期@4-bit
-2. 发送RD_CSR命令，验证读命令响应帧：40bit（status8+rdata32）=10周期@4-bit
-3. 发送AHB_WR32命令，验证写命令响应帧：8bit status_code=2周期@4-bit
-4. 发送AHB_RD32命令，验证读命令响应帧：40bit=10周期@4-bit
-期望结果：
-1. 响应帧周期数符合预期
-2. turnaround固定1周期
-coverage check点：
-直接用例覆盖，不收功能覆盖率</t>
-        </is>
-      </c>
-      <c r="D19" s="9" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="10" t="inlineStr">
-        <is>
-          <t>DV_TC_018</t>
-        </is>
-      </c>
-      <c r="B20" s="10" t="inlineStr">
-        <is>
-          <t>valid_opcode_test</t>
-        </is>
-      </c>
-      <c r="C20" s="24" t="inlineStr">
-        <is>
-          <t>配置条件：
-1. 模块复位完成，test_mode_i=1，en_i=1
-2. 配置LANE_MODE=01（4-bit模式）
-输入激励：
-1. 发送opcode=0x10命令（WR_CSR），reg_addr=0x04, wdata=0x00000001，验证WR_CSR路径
-2. 发送opcode=0x11命令（RD_CSR），reg_addr=0x00，验证RD_CSR路径
-3. 发送opcode=0x20命令（AHB_WR32），addr=0x00000100, wdata=0x12345678，验证AHB_WR32路径
-4. 发送opcode=0x21命令（AHB_RD32），addr=0x00000100，验证AHB_RD32路径
-期望结果：
-1. 正确译码：0x10→WR_CSR、0x11→RD_CSR、0x20→AHB_WR32、0x21→AHB_RD32
-2. 各命令返回正确的status_code和响应数据
-coverage check点：
-覆盖opcode=0x10、0x11、0x20、0x21</t>
-        </is>
-      </c>
-      <c r="D20" s="9" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="10" t="inlineStr">
-        <is>
-          <t>DV_TC_019</t>
-        </is>
-      </c>
-      <c r="B21" s="10" t="inlineStr">
-        <is>
-          <t>illegal_opcode_test</t>
-        </is>
-      </c>
-      <c r="C21" s="24" t="inlineStr">
-        <is>
-          <t>配置条件：
-1. 模块复位完成，test_mode_i=1，en_i=1
-2. 配置LANE_MODE=01（4-bit模式）
-输入激励：
-1. 发送opcode=0xFF命令，检查前置检查拒绝
-2. 发送opcode=0x00命令，检查前置检查拒绝
-3. 发送opcode=0x12命令（接近合法值但非法），检查拒绝
-期望结果：
-1. 非法opcode返回STS_BAD_OPCODE(0x02)，不发起任何访问
-2. 不产生CSR接口脉冲（csr_wr_en_o=0, csr_rd_en_o=0）
-3. 不产生AHB请求（htrans_o保持IDLE）
-coverage check点：
-覆盖非法opcode</t>
-        </is>
-      </c>
-      <c r="D21" s="9" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="10" t="inlineStr">
-        <is>
-          <t>DV_TC_020</t>
-        </is>
-      </c>
-      <c r="B22" s="10" t="inlineStr">
-        <is>
-          <t>opcode_random_test</t>
-        </is>
-      </c>
-      <c r="C22" s="24" t="inlineStr">
-        <is>
-          <t>配置条件：
-1. 模块复位完成，test_mode_i=1，en_i=1
-2. 随机配置lane_mode_i（2'b00/01）
-输入激励：
-1. 随机选择opcode：有效值0x10/0x11/0x20/0x21或非法值0x00~0x0F/0x12~0x1F/0x24~0xFF
-2. 对有效opcode附带合法参数（reg_addr/addr/wdata）
-3. 对非法opcode附带随机数据
-4. 重复执行N次（N≥20）
-期望结果：
-1. 有效opcode正确执行，返回status_code=STS_OK(0x00)
-2. 非法opcode返回STS_BAD_OPCODE(0x02)
-coverage check点：
-覆盖所有有效opcode（0x10、0x11、0x20、0x21）和部分非法opcode，覆盖lane_mode × opcode组合</t>
-        </is>
-      </c>
-      <c r="D22" s="9" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="10" t="inlineStr">
-        <is>
-          <t>DV_TC_021</t>
-        </is>
-      </c>
-      <c r="B23" s="10" t="inlineStr">
-        <is>
-          <t>lane_mode_config_test</t>
-        </is>
-      </c>
-      <c r="C23" s="24" t="inlineStr">
-        <is>
-          <t>配置条件：
-1. 模块复位完成，test_mode_i=1，en_i=1
-输入激励：
-1. 通过WR_CSR配置CTRL.LANE_MODE=00（1-bit模式），发送RD_CSR验证帧收发
-2. 通过WR_CSR配置CTRL.LANE_MODE=01（4-bit模式），发送RD_CSR验证帧收发
-3. 交替切换LANE_MODE，每次切换后发送命令验证
-期望结果：
-1. LANE_MODE切换后帧收发正确
-2. 1-bit模式使用pdi_i[0]/pdo_o[0]，4-bit模式使用pdi_i[3:0]/pdo_o[3:0]
-coverage check点：
-直接用例覆盖，不收功能覆盖率</t>
-        </is>
-      </c>
-      <c r="D23" s="9" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="10" t="inlineStr">
-        <is>
-          <t>DV_TC_022</t>
-        </is>
-      </c>
-      <c r="B24" s="10" t="inlineStr">
-        <is>
-          <t>soft_reset_test</t>
-        </is>
-      </c>
-      <c r="C24" s="24" t="inlineStr">
-        <is>
-          <t>配置条件：
-1. 模块复位完成，test_mode_i=1，en_i=1
-输入激励：
-1. 先发送AHB_WR32命令（opcode=0x20, addr=0x00000100, wdata=0xDEADBEEF）建立非默认状态
-2. 通过WR_CSR写入CTRL.SOFT_RST=1
-3. 检查协议上下文清零：front_state=IDLE，协议移位寄存器清零
-4. 检查lane模式恢复默认（1-bit）
-期望结果：
-1. SOFT_RST=1后协议上下文清零
-2. lane模式恢复默认1-bit模式
-coverage check点：
-直接用例覆盖，不收功能覆盖率</t>
-        </is>
-      </c>
-      <c r="D24" s="9" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="10" t="inlineStr">
-        <is>
-          <t>DV_TC_023</t>
-        </is>
-      </c>
-      <c r="B25" s="10" t="inlineStr">
-        <is>
-          <t>lane_switch_violation_test</t>
-        </is>
-      </c>
-      <c r="C25" s="24" t="inlineStr">
-        <is>
-          <t>配置条件：
-1. 模块复位完成，test_mode_i=1，en_i=1
-2. 设置lane_mode_i=2'b01（4-bit模式）
-输入激励：
-1. 拉低pcs_n_i开始发送RD_CSR命令（opcode=0x11, reg_addr=0x00）
-2. 在pcs_n_i=0事务期间切换lane_mode_i（从2'b01切到2'b00）
-3. 完成发送后检查响应数据
-期望结果：
-1. 帧数据损坏（移位宽度变化导致数据错位）
-2. 可能触发STS_BAD_OPCODE(0x02)或STS_FRAME_ERR(0x01)
-3. 模块不检测此违规，由结果错误暴露
-coverage check点：
-直接用例覆盖，不收功能覆盖率</t>
-        </is>
-      </c>
-      <c r="D25" s="9" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="10" t="inlineStr">
-        <is>
-          <t>DV_TC_024</t>
-        </is>
-      </c>
-      <c r="B26" s="10" t="inlineStr">
-        <is>
-          <t>status_polling_test</t>
-        </is>
-      </c>
-      <c r="C26" s="24" t="inlineStr">
-        <is>
-          <t>配置条件：
-1. 模块复位完成，test_mode_i=1，en_i=1
-输入激励：
-1. 发送RD_CSR命令（opcode=0x11, reg_addr=0x08）读取STATUS寄存器，检查BUSY=1/0
-2. 发送非法opcode(0xFF)触发错误，再读取STATUS检查CMD_ERR[2]=1
-3. 发送RD_CSR命令（opcode=0x11, reg_addr=0x0C）读取LAST_ERR寄存器，检查错误码=0x02
-4. 检查模块无独立中断输出端口
-期望结果：
-1. STATUS位域正确反映状态：BUSY/RESP_VALID/CMD_ERR/BUS_ERR/FRAME_ERR/IN_TEST_MODE/OUT_EN
-2. LAST_ERR存储最近错误码
-3. MVP版本无独立中断输出端口
-coverage check点：
-直接用例覆盖，不收功能覆盖率</t>
-        </is>
-      </c>
-      <c r="D26" s="9" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="10" t="inlineStr">
-        <is>
-          <t>DV_TC_025</t>
-        </is>
-      </c>
-      <c r="B27" s="10" t="inlineStr">
-        <is>
-          <t>error_priority_test</t>
-        </is>
-      </c>
-      <c r="C27" s="24" t="inlineStr">
-        <is>
-          <t>配置条件：
-1. 模块复位完成，test_mode_i=1，en_i=1
-输入激励：
-1. 发送WR_CSR命令（opcode=0x10），在接收8bit后提前拉高pcs_n_i → 返回STS_FRAME_ERR(0x01)
-2. 发送非法opcode(0xFF) → 返回STS_BAD_OPCODE(0x02)
-3. 设置test_mode_i=0，发送opcode=0x11 → 返回STS_NOT_IN_TEST(0x04)
-4. 设置test_mode_i=1，en_i=0，发送opcode=0x10 → 返回STS_DISABLED(0x08)
-5. 发送RD_CSR（opcode=0x11, reg_addr=0x40）→ 返回STS_BAD_REG(0x10)
-6. 发送AHB_RD32（opcode=0x21, addr=0x00000001）→ 返回STS_ALIGN_ERR(0x20)
-期望结果：
-1. 前置错误按优先级链返回：0x01 &gt; 0x02 &gt; 0x04 &gt; 0x08 &gt; 0x10 &gt; 0x20
-2. 每种错误码正确返回
-coverage check点：
-覆盖所有前置错误码（0x01、0x02、0x04、0x08、0x10、0x20）</t>
-        </is>
-      </c>
-      <c r="D27" s="9" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="10" t="inlineStr">
-        <is>
-          <t>DV_TC_026</t>
-        </is>
-      </c>
-      <c r="B28" s="10" t="inlineStr">
-        <is>
-          <t>ahb_error_test</t>
-        </is>
-      </c>
-      <c r="C28" s="24" t="inlineStr">
-        <is>
-          <t>配置条件：
-1. 模块复位完成，test_mode_i=1，en_i=1
-2. 配置LANE_MODE=01（4-bit模式）
-输入激励：
-1. 发送AHB_RD32命令（opcode=0x21, addr=0x00000100）
-2. 配置AHB Slave在数据相返回hresp_i=1
-3. 检查响应帧status_code
-期望结果：
-1. 返回STS_AHB_ERR(0x40)
-2. 不返回读数据
-coverage check点：
-直接用例覆盖，不收功能覆盖率</t>
-        </is>
-      </c>
-      <c r="D28" s="9" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="10" t="inlineStr">
-        <is>
-          <t>DV_TC_027</t>
-        </is>
-      </c>
-      <c r="B29" s="10" t="inlineStr">
-        <is>
-          <t>timeout_test</t>
-        </is>
-      </c>
-      <c r="C29" s="24" t="inlineStr">
-        <is>
-          <t>配置条件：
-1. 模块复位完成，test_mode_i=1，en_i=1
-2. 配置LANE_MODE=01（4-bit模式）
-输入激励：
-1. 发送AHB_RD32命令（opcode=0x21, addr=0x00000100）
-2. 配置hready_i持续为0超过256个clk_i周期
-3. 检查超时后的响应
-期望结果：
-1. 超时（256周期）返回STS_AHB_ERR(0x40)
-2. 9-bit超时计数器从0计数至BUS_TIMEOUT_CYCLES-1(255)触发超时
-coverage check点：
-直接用例覆盖，不收功能覆盖率</t>
-        </is>
-      </c>
-      <c r="D29" s="9" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="10" t="inlineStr">
-        <is>
-          <t>DV_TC_028</t>
-        </is>
-      </c>
-      <c r="B30" s="10" t="inlineStr">
-        <is>
-          <t>error_injection_random_test</t>
-        </is>
-      </c>
-      <c r="C30" s="24" t="inlineStr">
-        <is>
-          <t>配置条件：
-1. 模块复位完成，test_mode_i=1，en_i=1
-输入激励：
-1. 随机选择错误类型并注入：
-   - 非法opcode（随机选择0x00~0x0F或0x12~0xFF）验证STS_BAD_OPCODE(0x02)
-   - 非法CSR地址（reg_addr随机&gt;=0x40）验证STS_BAD_REG(0x10)
-   - 非对齐地址（addr随机设置addr[1:0]!=0）验证STS_ALIGN_ERR(0x20)
-   - AHB错误响应（force hresp_i=1）验证STS_AHB_ERR(0x40)
-2. 每种错误类型重复执行N次（N≥5）
-期望结果：
-1. 各错误场景返回正确错误码
-2. 前置错误不发起CSR/AHB访问
-3. AHB错误在执行期发生
-coverage check点：
-覆盖所有状态码（0x00、0x01、0x02、0x04、0x08、0x10、0x20、0x40），覆盖opcode × status_code交叉</t>
-        </is>
-      </c>
-      <c r="D30" s="9" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="10" t="inlineStr">
-        <is>
-          <t>DV_TC_029</t>
-        </is>
-      </c>
-      <c r="B31" s="10" t="inlineStr">
-        <is>
-          <t>idle_power_test</t>
-        </is>
-      </c>
-      <c r="C31" s="24" t="inlineStr">
-        <is>
-          <t>配置条件：
-1. 模块复位完成
-输入激励：
-1. pcs_n_i=1保持空闲态超过100周期
-2. 检查RX/TX移位寄存器和超时计数器是否不翻转
-3. 再发送一条命令后回到空闲态，再次检查
-期望结果：
-1. 空闲态：接收/发送移位寄存器不更新，超时计数器不工作
-2. 仅在RX/TX/WAIT_AHB状态翻转关键寄存器
-coverage check点：
-直接用例覆盖，不收功能覆盖率</t>
-        </is>
-      </c>
-      <c r="D31" s="9" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="10" t="inlineStr">
-        <is>
-          <t>DV_TC_030</t>
-        </is>
-      </c>
-      <c r="B32" s="10" t="inlineStr">
-        <is>
-          <t>ahb_idle_test</t>
-        </is>
-      </c>
-      <c r="C32" s="24" t="inlineStr">
-        <is>
-          <t>配置条件：
-1. 模块复位完成，test_mode_i=0
-输入激励：
-1. 发送RD_CSR命令（opcode=0x11, reg_addr=0x00）
-2. 检查AHB输出htrans_o是否保持IDLE
-3. 设置test_mode_i=1但无有效任务，检查htrans_o
-期望结果：
-1. test_mode_i=0：AHB输出保持IDLE（htrans_o=2'b00）
-2. 无有效任务时：htrans_o保持IDLE
-coverage check点：
-直接用例覆盖，不收功能覆盖率</t>
-        </is>
-      </c>
-      <c r="D32" s="9" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="10" t="inlineStr">
-        <is>
-          <t>DV_TC_031</t>
-        </is>
-      </c>
-      <c r="B33" s="10" t="inlineStr">
-        <is>
-          <t>throughput_test</t>
-        </is>
-      </c>
-      <c r="C33" s="24" t="inlineStr">
-        <is>
-          <t>配置条件：
-1. 模块复位完成，test_mode_i=1，en_i=1
-2. clk_i配置为100MHz
-输入激励：
-1. AHB_RD32@4-bit：测量RX(10周期)+译码(2周期)+AHB返回(N周期)+TA(1周期)+TX(10周期)
-2. AHB_WR32@4-bit：测量RX(18周期)+执行(2周期)+TA(1周期)+TX(2周期)
-3. RD_CSR@1-bit：测量RX(16周期)+backend+TA(1周期)+TX(40周期)
-期望结果：
-1. 4-bit模式AHB_RD32最小延时约23~24周期
-2. 4-bit模式AHB_WR32最小延时约23周期
-3. 1-bit模式延时约为4-bit的4倍
-coverage check点：
-直接用例覆盖，不收功能覆盖率</t>
-        </is>
-      </c>
-      <c r="D33" s="9" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="10" t="inlineStr">
-        <is>
-          <t>DV_TC_032</t>
-        </is>
-      </c>
-      <c r="B34" s="10" t="inlineStr">
-        <is>
-          <t>address_alignment_test</t>
-        </is>
-      </c>
-      <c r="C34" s="24" t="inlineStr">
-        <is>
-          <t>配置条件：
-1. 模块复位完成，test_mode_i=1，en_i=1
-2. 配置LANE_MODE=01（4-bit模式）
-输入激励：
-1. 发送AHB_WR32命令（opcode=0x20），addr=0x00000001（非4-byte对齐，addr[1:0]=01）
-2. 发送AHB_RD32命令（opcode=0x21），addr=0x00000002（非4-byte对齐，addr[1:0]=10）
-3. 发送AHB_WR32命令（opcode=0x20），addr=0x00000003（非4-byte对齐，addr[1:0]=11）
-4. 发送AHB_WR32命令（opcode=0x20），addr=0x00000100（4-byte对齐，addr[1:0]=00）
-期望结果：
-1. 非对齐地址返回STS_ALIGN_ERR(0x20)，不发起AHB访问
-2. 对齐地址正常执行，返回STS_OK(0x00)
-coverage check点：
-直接用例覆盖，不收功能覆盖率</t>
-        </is>
-      </c>
-      <c r="D34" s="9" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="10" t="inlineStr">
-        <is>
-          <t>DV_TC_033</t>
-        </is>
-      </c>
-      <c r="B35" s="10" t="inlineStr">
-        <is>
-          <t>dfx_observability_test</t>
-        </is>
-      </c>
-      <c r="C35" s="24" t="inlineStr">
-        <is>
-          <t>配置条件：
-1. 模块复位完成，test_mode_i=1，en_i=1
-输入激励：
-1. 发送RD_CSR命令（opcode=0x11, reg_addr=0x00），检查front_state从IDLE→ISSUE→WAIT_RESP→TA→TX→IDLE
-2. 发送AHB_WR32命令（opcode=0x20, addr=0x00000100, wdata=0x12345678），检查back_state和axi_state跳转
-3. 发送非法opcode(0xFF)触发错误，检查status_code和LAST_ERR
-期望结果：
-1. 所有调试可观测点可正确反映内部状态
-2. 状态机状态变化符合协议流程
-3. 错误状态下可观测到错误码和原因
-coverage check点：
-直接用例覆盖，不收功能覆盖率</t>
-        </is>
-      </c>
-      <c r="D35" s="9" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="10" t="inlineStr">
-        <is>
-          <t>DV_TC_034</t>
-        </is>
-      </c>
-      <c r="B36" s="10" t="inlineStr">
-        <is>
-          <t>csr_access_path_test</t>
-        </is>
-      </c>
-      <c r="C36" s="24" t="inlineStr">
-        <is>
-          <t>配置条件：
-1. 模块复位完成，test_mode_i=1，en_i=1
-输入激励：
-1. 发送WR_CSR命令（opcode=0x10, reg_addr=0x04, wdata=0x00000001）访问CTRL寄存器
-2. 发送RD_CSR命令（opcode=0x11, reg_addr=0x08）读取STATUS寄存器
-3. 检查CSR访问是否通过协议命令完成，不经过AHB
-期望结果：
-1. CSR访问不经过AHB（htrans_o保持IDLE）
-2. CSR通过协议命令访问（opcode=0x10/0x11）
-coverage check点：
-直接用例覆盖，不收功能覆盖率</t>
-        </is>
-      </c>
-      <c r="D36" s="9" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="10" t="inlineStr">
-        <is>
-          <t>DV_TC_035</t>
-        </is>
-      </c>
-      <c r="B37" s="10" t="inlineStr">
-        <is>
-          <t>ahb_access_path_test</t>
-        </is>
-      </c>
-      <c r="C37" s="24" t="inlineStr">
-        <is>
-          <t>配置条件：
-1. 模块复位完成，test_mode_i=1，en_i=1
-输入激励：
-1. 发送AHB_WR32命令（opcode=0x20, addr=0x00000100, wdata=0xDEADBEEF）
-2. 发送AHB_RD32命令（opcode=0x21, addr=0x00000100）
-3. 检查AHB Master接口信号
-期望结果：
-1. AHB Master访问使用32bit地址、word访问粒度
-2. hsize_o=3'b010(WORD)，haddr_o[1:0]=2'b00
-coverage check点：
-直接用例覆盖，不收功能覆盖率</t>
-        </is>
-      </c>
-      <c r="D37" s="9" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="10" t="inlineStr">
-        <is>
-          <t>DV_TC_036</t>
-        </is>
-      </c>
-      <c r="B38" s="10" t="inlineStr">
-        <is>
-          <t>ahb_single_test</t>
-        </is>
-      </c>
-      <c r="C38" s="24" t="inlineStr">
-        <is>
-          <t>配置条件：
-1. 模块复位完成，test_mode_i=1，en_i=1
-2. AHB Slave配置hready_i=1正常响应
-输入激励：
-1. 发送AHB_WR32命令（opcode=0x20, addr=0x00000100, wdata=0x12345678）：验证T1地址相驱动haddr+hwrite+htrans=NONSEQ，T2数据相驱动hwdata
-2. 发送AHB_RD32命令（opcode=0x21, addr=0x00000100）：验证T1地址相驱动haddr+hwrite=0+htrans=NONSEQ，T2采样hrdata
-期望结果：
-1. 写操作：T1驱动haddr与NONSEQ，T2驱动hwdata
-2. 读操作：T1驱动haddr与NONSEQ，T2从机驱动hrdata
-3. haddr与hwdata/hrdata错开1拍
-coverage check点：
-直接用例覆盖，不收功能覆盖率</t>
-        </is>
-      </c>
-      <c r="D38" s="9" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="10" t="inlineStr">
-        <is>
-          <t>DV_TC_037</t>
-        </is>
-      </c>
-      <c r="B39" s="10" t="inlineStr">
-        <is>
-          <t>ahb_2phase_timing_test</t>
-        </is>
-      </c>
-      <c r="C39" s="24" t="inlineStr">
-        <is>
-          <t>配置条件：
-1. 模块复位完成，test_mode_i=1，en_i=1
-2. 配置LANE_MODE=01（4-bit模式）
-输入激励：
-1. 发送AHB_RD32命令（opcode=0x21, addr=0x00000100）
-2. 精确测量地址相（AXI_REQ状态）和数据相（AXI_WAIT状态）的1拍overlap
-期望结果：
-1. haddr与hrdata错开1拍
-2. T1: htrans_o=NONSEQ(2'b10)，T2: htrans_o=IDLE(2'b00)
-coverage check点：
-直接用例覆盖，不收功能覆盖率</t>
-        </is>
-      </c>
-      <c r="D39" s="9" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="10" t="inlineStr">
-        <is>
-          <t>DV_TC_038</t>
-        </is>
-      </c>
-      <c r="B40" s="10" t="inlineStr">
-        <is>
-          <t>ahb_fixed_param_test</t>
-        </is>
-      </c>
-      <c r="C40" s="24" t="inlineStr">
-        <is>
-          <t>配置条件：
-1. 模块复位完成，test_mode_i=1，en_i=1
-输入激励：
-1. 发送AHB_WR32命令（opcode=0x20, addr=0x00000100, wdata=0x00000001）
-2. 检查hsize_o=3'b010(WORD)
-3. 检查hburst_o=3'b000(SINGLE)
-4. 发送AHB_RD32命令，再次验证固定参数
-期望结果：
-1. hsize_o固定3'b010(WORD)
-2. hburst_o固定3'b000(SINGLE)
-coverage check点：
-直接用例覆盖，不收功能覆盖率</t>
-        </is>
-      </c>
-      <c r="D40" s="9" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="10" t="inlineStr">
-        <is>
-          <t>DV_TC_039</t>
-        </is>
-      </c>
-      <c r="B41" s="10" t="inlineStr">
-        <is>
-          <t>ahb_error_response_test</t>
-        </is>
-      </c>
-      <c r="C41" s="24" t="inlineStr">
-        <is>
-          <t>配置条件：
-1. 模块复位完成，test_mode_i=1，en_i=1
-输入激励：
-1. 发送AHB_WR32命令（opcode=0x20, addr=0x00000100, wdata=0xDEADBEEF）
-2. 配置AHB Slave在数据相返回hresp_i=1
-3. 发送AHB_RD32命令（opcode=0x21, addr=0x00000100）
-4. 再次配置Slave返回hresp_i=1
-期望结果：
-1. hresp_i=1返回STS_AHB_ERR(0x40)
-2. 读命令和写命令均正确上报AHB错误
-coverage check点：
-直接用例覆盖，不收功能覆盖率</t>
-        </is>
-      </c>
-      <c r="D41" s="9" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="10" t="inlineStr">
-        <is>
-          <t>DV_TC_040</t>
-        </is>
-      </c>
-      <c r="B42" s="10" t="inlineStr">
-        <is>
-          <t>lane_opcode_cross_test</t>
-        </is>
-      </c>
-      <c r="C42" s="24" t="inlineStr">
-        <is>
-          <t>配置条件：
-1. 模块复位完成，test_mode_i=1，en_i=1
-输入激励：
-1. 使用嵌套循环遍历所有组合：
-   for lane_mode in [2'b00, 2'b01]:
-       for opcode in [0x10, 0x11, 0x20, 0x21]:
-           配置对应lane_mode
-           发送对应opcode命令
-           检查响应
-期望结果：
-1. 所有2×4=8种组合正确执行，返回status_code=STS_OK(0x00)
-2. 无遗漏组合
-coverage check点：
-覆盖lane_mode × opcode所有组合（2×4=8种），功能模型：遍历lane_mode_i[1:0]与opcode_latched_q[7:0]所有合法组合</t>
-        </is>
-      </c>
-      <c r="D42" s="9" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="10" t="inlineStr">
-        <is>
-          <t>DV_TC_041</t>
-        </is>
-      </c>
-      <c r="B43" s="10" t="inlineStr">
-        <is>
-          <t>all_opcode_success_test</t>
-        </is>
-      </c>
-      <c r="C43" s="24" t="inlineStr">
-        <is>
-          <t>配置条件：
-1. 模块复位完成，test_mode_i=1，en_i=1
-输入激励：
-1. 发送WR_CSR（opcode=0x10, reg_addr=0x04, wdata=0x00000001）验证成功路径
-2. 发送RD_CSR（opcode=0x11, reg_addr=0x00）验证成功路径
-3. 发送AHB_WR32（opcode=0x20, addr=0x00000100, wdata=0x12345678）验证成功路径
-4. 发送AHB_RD32（opcode=0x21, addr=0x00000100）验证成功路径
-期望结果：
-1. 所有opcode返回status_code=STS_OK(0x00)
-2. CSR命令正确触发csr_wr_en_o/csr_rd_en_o
-3. AHB命令正确发起AHB事务
-coverage check点：
-覆盖opcode=0x10、0x11、0x20、0x21成功场景，功能模型：覆盖opcode_latched_q所有合法取值的STS_OK路径</t>
-        </is>
-      </c>
       <c r="D43" s="9" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="10" t="inlineStr">
         <is>
-          <t>DV_TC_042</t>
+          <t>TC_042</t>
         </is>
       </c>
       <c r="B44" s="10" t="inlineStr">
         <is>
-          <t>comprehensive_random_test</t>
-        </is>
-      </c>
-      <c r="C44" s="24" t="inlineStr">
+          <t>test_ahb_write</t>
+        </is>
+      </c>
+      <c r="C44" s="11" t="inlineStr">
         <is>
           <t>配置条件：
-1. 模块复位完成，test_mode_i=1，en_i=1
+1.模块复位完成，test_mode_i=1，en_i=1；
+2.lane_mode_i=2'b01；
+3.AHB Slave配置正常响应；
 输入激励：
-1. 随机配置lane_mode_i（2'b00/01）
-2. 随机选择opcode（有效0x10/0x11/0x20/0x21或非法0x00~0x0F/0x24~0xFF）
-3. 对有效opcode附带随机参数：随机reg_addr(0x00~0x3F有效或&gt;=0x40无效)、随机addr(对齐或非对齐)、随机wdata
-4. 随机注入错误：force hresp_i=1、force hready_i=0超过256周期
-5. 重复执行N次（N≥100），每次随机配置
+1.发送AHB_WR32命令（opcode=0x20，addr=0x10000000，wdata=0xDEADBEEF）；
+2.观察AHB 2-phase流水：
+   - T1（地址相）：htrans_o=2'b10(NONSEQ)，haddr_o=0x10000000，hwrite_o=1，hsize_o=3'b010，hburst_o=3'b000
+   - T2（数据相）：hwdata_o=0xDEADBEEF有效，htrans_o回到IDLE
+3.检查haddr与hwdata错开1拍；
+4.检查在hready_i=1时一拍完成；
+5.检查响应status_code=STS_OK(0x00)；
 期望结果：
-1. 成功场景：status_code=STS_OK(0x00)
-2. 失败场景：返回对应错误码
-3. 所有配置组合均被覆盖
+1.地址相：htrans=NONSEQ，驱动haddr+hwrite+hsize+hburst；
+2.数据相：驱动hwdata，htrans回到IDLE；
+3.haddr与hwdata必然错开1拍；
+4.hsize=3'b010(WORD)，hburst=3'b000(SINGLE)固定；
+5.写操作成功，status_code=0x00；
 coverage check点：
-覆盖lane_mode所有取值（2'b00, 2'b01）、所有有效opcode（0x10, 0x11, 0x20, 0x21）、部分非法opcode、所有状态码（0x00, 0x01, 0x02, 0x04, 0x08, 0x10, 0x20, 0x40），功能模型：lane_mode_i × opcode_latched_q × status_code三维交叉覆盖</t>
+对AHB写时序采集功能覆盖率</t>
         </is>
       </c>
       <c r="D44" s="9" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="10" t="n"/>
-      <c r="B45" s="10" t="n"/>
-      <c r="C45" s="24" t="n"/>
+      <c r="A45" s="10" t="inlineStr">
+        <is>
+          <t>TC_043</t>
+        </is>
+      </c>
+      <c r="B45" s="10" t="inlineStr">
+        <is>
+          <t>test_ahb_read</t>
+        </is>
+      </c>
+      <c r="C45" s="11" t="inlineStr">
+        <is>
+          <t>配置条件：
+1.模块复位完成，test_mode_i=1，en_i=1；
+2.lane_mode_i=2'b01；
+3.AHB Slave配置正常响应并提供读数据；
+输入激励：
+1.发送AHB_RD32命令（opcode=0x21，addr=0x20000000）；
+2.观察AHB 2-phase流水：
+   - T1（地址相）：htrans_o=NONSEQ，haddr_o=0x20000000，hwrite_o=0
+   - T2（数据相）：采样hrdata_i，htrans_o=IDLE
+3.检查haddr与hrdata错开1拍；
+4.验证Slave在数据相提供hrdata；
+5.检查响应帧包含正确rdata；
+期望结果：
+1.地址相：htrans=NONSEQ，驱动haddr，hwrite=0；
+2.数据相：采样hrdata，htrans=IDLE；
+3.haddr与hrdata错开1拍；
+4.rdata正确返回在响应帧中；
+5.status_code=STS_OK(0x00)；
+coverage check点：
+对AHB读时序采集功能覆盖率</t>
+        </is>
+      </c>
       <c r="D45" s="9" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="10" t="n"/>
-      <c r="B46" s="10" t="n"/>
-      <c r="C46" s="24" t="n"/>
+      <c r="A46" s="10" t="inlineStr">
+        <is>
+          <t>TC_044</t>
+        </is>
+      </c>
+      <c r="B46" s="10" t="inlineStr">
+        <is>
+          <t>test_ahb_2phase_pipeline</t>
+        </is>
+      </c>
+      <c r="C46" s="11" t="inlineStr">
+        <is>
+          <t>配置条件：
+1.模块复位完成，test_mode_i=1，en_i=1；
+2.lane_mode_i=2'b01；
+输入激励：
+1.连续发送AHB_WR32和AHB_RD32命令；
+2.观察每个命令的AHB 2-phase流水；
+3.检查固定参数：
+   - hsize_o=3'b010(WORD)
+   - hburst_o=3'b000(SINGLE)
+   - 不支持BUSY传输类型
+4.验证地址相与数据相overlap 1拍；
+5.验证hready_i等待扩展数据相；
+期望结果：
+1.每个AHB事务为独立的SINGLE传输；
+2.hsize固定WORD，hburst固定SINGLE；
+3.地址相(htrans=NONSEQ)与数据相(hwdata/hrdata)错开1拍；
+4.hready_i=0时数据相扩展等待；
+5.MVP不支持连续Burst，每事务独立；
+coverage check点：
+对AHB 2-phase流水的固定参数采集功能覆盖率</t>
+        </is>
+      </c>
       <c r="D46" s="9" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="10" t="n"/>
-      <c r="B47" s="10" t="n"/>
-      <c r="C47" s="24" t="n"/>
+      <c r="A47" s="10" t="inlineStr">
+        <is>
+          <t>TC_045</t>
+        </is>
+      </c>
+      <c r="B47" s="10" t="inlineStr">
+        <is>
+          <t>test_ahb_error_recovery</t>
+        </is>
+      </c>
+      <c r="C47" s="11" t="inlineStr">
+        <is>
+          <t>配置条件：
+1.模块复位完成，test_mode_i=1，en_i=1；
+2.lane_mode_i随机选择（1-bit或4-bit）；
+输入激励：
+1.发送AHB_RD32命令；
+2.配置Slave返回hresp_i=1触发错误；
+3.观察AXI FSM：AXI_WAIT→AXI_ERR→AXI_IDLE；
+4.检查status_code=STS_AHB_ERR(0x40)；
+5.恢复Slave正常响应；
+6.发送新命令（随机类型）验证模块恢复；
+7.重复执行N次（N≥10），覆盖各种lane_mode和命令类型；
+期望结果：
+1.hresp_i=1后FSM正确进入AXI_ERR状态；
+2.AHB输出恢复空闲：htrans=IDLE；
+3.错误恢复后新命令正常响应；
+4.恢复机制可靠；
+coverage check点：
+随机测试，覆盖AHB错误恢复场景的功能覆盖率</t>
+        </is>
+      </c>
       <c r="D47" s="9" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="10" t="n"/>
       <c r="B48" s="10" t="n"/>
-      <c r="C48" s="24" t="n"/>
+      <c r="C48" s="11" t="n"/>
       <c r="D48" s="9" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="10" t="n"/>
       <c r="B49" s="10" t="n"/>
-      <c r="C49" s="24" t="n"/>
+      <c r="C49" s="11" t="n"/>
       <c r="D49" s="9" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="10" t="n"/>
       <c r="B50" s="10" t="n"/>
-      <c r="C50" s="24" t="n"/>
+      <c r="C50" s="11" t="n"/>
       <c r="D50" s="9" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="10" t="n"/>
       <c r="B51" s="10" t="n"/>
-      <c r="C51" s="24" t="n"/>
+      <c r="C51" s="11" t="n"/>
       <c r="D51" s="9" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="10" t="n"/>
       <c r="B52" s="10" t="n"/>
-      <c r="C52" s="24" t="n"/>
+      <c r="C52" s="11" t="n"/>
       <c r="D52" s="9" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="10" t="n"/>
       <c r="B53" s="10" t="n"/>
-      <c r="C53" s="24" t="n"/>
+      <c r="C53" s="11" t="n"/>
       <c r="D53" s="9" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="10" t="n"/>
       <c r="B54" s="10" t="n"/>
-      <c r="C54" s="24" t="n"/>
+      <c r="C54" s="11" t="n"/>
       <c r="D54" s="9" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="10" t="n"/>
       <c r="B55" s="10" t="n"/>
-      <c r="C55" s="24" t="n"/>
+      <c r="C55" s="11" t="n"/>
       <c r="D55" s="9" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="10" t="n"/>
       <c r="B56" s="10" t="n"/>
-      <c r="C56" s="24" t="n"/>
+      <c r="C56" s="11" t="n"/>
       <c r="D56" s="9" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="10" t="n"/>
       <c r="B57" s="10" t="n"/>
-      <c r="C57" s="24" t="n"/>
+      <c r="C57" s="11" t="n"/>
       <c r="D57" s="9" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n"/>
       <c r="B58" s="2" t="n"/>
-      <c r="C58" s="24" t="n"/>
+      <c r="C58" s="11" t="n"/>
       <c r="D58" s="3" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n"/>
       <c r="B59" s="2" t="n"/>
-      <c r="C59" s="24" t="n"/>
+      <c r="C59" s="11" t="n"/>
       <c r="D59" s="3" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="3" t="n"/>
       <c r="B60" s="3" t="n"/>
-      <c r="C60" s="24" t="n"/>
+      <c r="C60" s="11" t="n"/>
       <c r="D60" s="3" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="3" t="n"/>
       <c r="B61" s="3" t="n"/>
-      <c r="C61" s="24" t="n"/>
+      <c r="C61" s="11" t="n"/>
       <c r="D61" s="3" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="3" t="n"/>
       <c r="B62" s="3" t="n"/>
-      <c r="C62" s="24" t="n"/>
+      <c r="C62" s="11" t="n"/>
       <c r="D62" s="3" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="3" t="n"/>
       <c r="B63" s="3" t="n"/>
-      <c r="C63" s="24" t="n"/>
+      <c r="C63" s="11" t="n"/>
       <c r="D63" s="3" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="3" t="n"/>
       <c r="B64" s="3" t="n"/>
-      <c r="C64" s="24" t="n"/>
+      <c r="C64" s="11" t="n"/>
       <c r="D64" s="3" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="3" t="n"/>
       <c r="B65" s="3" t="n"/>
-      <c r="C65" s="24" t="n"/>
+      <c r="C65" s="11" t="n"/>
       <c r="D65" s="3" t="n"/>
     </row>
   </sheetData>
